--- a/data/brand/research/사이즈수집.xlsx
+++ b/data/brand/research/사이즈수집.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_AB2EE886377E835D65E88F615FB26BF6B25D546F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1104CDA6-E958-4288-8F7F-03F42652BD06}"/>
+  <xr:revisionPtr revIDLastSave="129" documentId="11_AB2EE886377E835D65E88F615FB26BF6B25D546F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F15FD1F-4E00-4541-97F4-A6099AF9A42B}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1185" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7640" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8214" uniqueCount="554">
   <si>
     <t>브랜드</t>
   </si>
@@ -1652,6 +1652,48 @@
   </si>
   <si>
     <t>남성 아이스큐브 반팔 티</t>
+  </si>
+  <si>
+    <t>와이드 히든 밴딩 슬랙스</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>없음</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>밴딩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사이드밴딩</t>
+  </si>
+  <si>
+    <t>풀밴딩</t>
+  </si>
+  <si>
+    <t>사이드밴딩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>풀밴딩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[4WAY STRETCH] 와이드핏 밴딩 슬랙스</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>와이드핏 셋업 팬츠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경량 에센셜 세미와이드핏 데님 팬츠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒷밴딩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1745,6 +1787,10 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -25028,7 +25074,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L574"/>
+  <dimension ref="A1:M574"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -25039,10 +25085,11 @@
     <col min="7" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="26" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -25076,11 +25123,14 @@
       <c r="K1" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -25115,10 +25165,13 @@
         <v>20</v>
       </c>
       <c r="L2" t="s">
+        <v>546</v>
+      </c>
+      <c r="M2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -25153,10 +25206,13 @@
         <v>20.3</v>
       </c>
       <c r="L3" t="s">
+        <v>546</v>
+      </c>
+      <c r="M3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -25191,10 +25247,13 @@
         <v>20.5</v>
       </c>
       <c r="L4" t="s">
+        <v>546</v>
+      </c>
+      <c r="M4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -25229,10 +25288,13 @@
         <v>20.8</v>
       </c>
       <c r="L5" t="s">
+        <v>546</v>
+      </c>
+      <c r="M5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -25267,10 +25329,13 @@
         <v>21</v>
       </c>
       <c r="L6" t="s">
+        <v>546</v>
+      </c>
+      <c r="M6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -25305,10 +25370,13 @@
         <v>21.3</v>
       </c>
       <c r="L7" t="s">
+        <v>546</v>
+      </c>
+      <c r="M7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -25343,10 +25411,13 @@
         <v>21.5</v>
       </c>
       <c r="L8" t="s">
+        <v>546</v>
+      </c>
+      <c r="M8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -25381,10 +25452,13 @@
         <v>21.8</v>
       </c>
       <c r="L9" t="s">
+        <v>546</v>
+      </c>
+      <c r="M9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -25419,10 +25493,13 @@
         <v>22</v>
       </c>
       <c r="L10" t="s">
+        <v>546</v>
+      </c>
+      <c r="M10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -25457,10 +25534,13 @@
         <v>22.5</v>
       </c>
       <c r="L11" t="s">
+        <v>546</v>
+      </c>
+      <c r="M11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -25495,10 +25575,13 @@
         <v>23</v>
       </c>
       <c r="L12" t="s">
+        <v>546</v>
+      </c>
+      <c r="M12" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -25533,10 +25616,13 @@
         <v>23.5</v>
       </c>
       <c r="L13" t="s">
+        <v>546</v>
+      </c>
+      <c r="M13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -25571,10 +25657,13 @@
         <v>24</v>
       </c>
       <c r="L14" t="s">
+        <v>546</v>
+      </c>
+      <c r="M14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -25609,10 +25698,13 @@
         <v>25.5</v>
       </c>
       <c r="L15" t="s">
+        <v>546</v>
+      </c>
+      <c r="M15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -25647,10 +25739,13 @@
         <v>25.8</v>
       </c>
       <c r="L16" t="s">
+        <v>546</v>
+      </c>
+      <c r="M16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -25685,10 +25780,13 @@
         <v>26</v>
       </c>
       <c r="L17" t="s">
+        <v>546</v>
+      </c>
+      <c r="M17" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -25723,10 +25821,13 @@
         <v>26.3</v>
       </c>
       <c r="L18" t="s">
+        <v>546</v>
+      </c>
+      <c r="M18" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -25761,10 +25862,13 @@
         <v>26.5</v>
       </c>
       <c r="L19" t="s">
+        <v>546</v>
+      </c>
+      <c r="M19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -25799,10 +25903,13 @@
         <v>26.8</v>
       </c>
       <c r="L20" t="s">
+        <v>546</v>
+      </c>
+      <c r="M20" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -25837,10 +25944,13 @@
         <v>27</v>
       </c>
       <c r="L21" t="s">
+        <v>546</v>
+      </c>
+      <c r="M21" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -25875,10 +25985,13 @@
         <v>27.3</v>
       </c>
       <c r="L22" t="s">
+        <v>546</v>
+      </c>
+      <c r="M22" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -25913,10 +26026,13 @@
         <v>27.5</v>
       </c>
       <c r="L23" t="s">
+        <v>546</v>
+      </c>
+      <c r="M23" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -25951,10 +26067,13 @@
         <v>28</v>
       </c>
       <c r="L24" t="s">
+        <v>546</v>
+      </c>
+      <c r="M24" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -25989,10 +26108,13 @@
         <v>28.5</v>
       </c>
       <c r="L25" t="s">
+        <v>546</v>
+      </c>
+      <c r="M25" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -26027,10 +26149,13 @@
         <v>29</v>
       </c>
       <c r="L26" t="s">
+        <v>546</v>
+      </c>
+      <c r="M26" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -26065,10 +26190,13 @@
         <v>29.5</v>
       </c>
       <c r="L27" t="s">
+        <v>546</v>
+      </c>
+      <c r="M27" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -26079,7 +26207,7 @@
         <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>188</v>
+        <v>543</v>
       </c>
       <c r="E28" t="s">
         <v>172</v>
@@ -26103,10 +26231,13 @@
         <v>22.5</v>
       </c>
       <c r="L28" t="s">
+        <v>546</v>
+      </c>
+      <c r="M28" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -26117,7 +26248,7 @@
         <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>188</v>
+        <v>543</v>
       </c>
       <c r="E29" t="s">
         <v>173</v>
@@ -26141,10 +26272,13 @@
         <v>22.8</v>
       </c>
       <c r="L29" t="s">
+        <v>546</v>
+      </c>
+      <c r="M29" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -26179,10 +26313,13 @@
         <v>23</v>
       </c>
       <c r="L30" t="s">
+        <v>546</v>
+      </c>
+      <c r="M30" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -26217,10 +26354,13 @@
         <v>23.3</v>
       </c>
       <c r="L31" t="s">
+        <v>546</v>
+      </c>
+      <c r="M31" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -26255,10 +26395,13 @@
         <v>23.5</v>
       </c>
       <c r="L32" t="s">
+        <v>546</v>
+      </c>
+      <c r="M32" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -26293,10 +26436,13 @@
         <v>23.8</v>
       </c>
       <c r="L33" t="s">
+        <v>546</v>
+      </c>
+      <c r="M33" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -26331,10 +26477,13 @@
         <v>24</v>
       </c>
       <c r="L34" t="s">
+        <v>546</v>
+      </c>
+      <c r="M34" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -26369,10 +26518,13 @@
         <v>24.3</v>
       </c>
       <c r="L35" t="s">
+        <v>546</v>
+      </c>
+      <c r="M35" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -26407,10 +26559,13 @@
         <v>24.5</v>
       </c>
       <c r="L36" t="s">
+        <v>546</v>
+      </c>
+      <c r="M36" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>34</v>
       </c>
@@ -26445,10 +26600,13 @@
         <v>25</v>
       </c>
       <c r="L37" t="s">
+        <v>546</v>
+      </c>
+      <c r="M37" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>34</v>
       </c>
@@ -26483,10 +26641,13 @@
         <v>25.5</v>
       </c>
       <c r="L38" t="s">
+        <v>546</v>
+      </c>
+      <c r="M38" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>34</v>
       </c>
@@ -26521,10 +26682,13 @@
         <v>26</v>
       </c>
       <c r="L39" t="s">
+        <v>546</v>
+      </c>
+      <c r="M39" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>34</v>
       </c>
@@ -26559,10 +26723,13 @@
         <v>26.5</v>
       </c>
       <c r="L40" t="s">
+        <v>546</v>
+      </c>
+      <c r="M40" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>34</v>
       </c>
@@ -26597,10 +26764,13 @@
         <v>19.5</v>
       </c>
       <c r="L41" t="s">
+        <v>546</v>
+      </c>
+      <c r="M41" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>34</v>
       </c>
@@ -26635,10 +26805,13 @@
         <v>19.8</v>
       </c>
       <c r="L42" t="s">
+        <v>546</v>
+      </c>
+      <c r="M42" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -26673,10 +26846,13 @@
         <v>20</v>
       </c>
       <c r="L43" t="s">
+        <v>546</v>
+      </c>
+      <c r="M43" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>34</v>
       </c>
@@ -26711,10 +26887,13 @@
         <v>20.2</v>
       </c>
       <c r="L44" t="s">
+        <v>546</v>
+      </c>
+      <c r="M44" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>34</v>
       </c>
@@ -26749,10 +26928,13 @@
         <v>20.5</v>
       </c>
       <c r="L45" t="s">
+        <v>546</v>
+      </c>
+      <c r="M45" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>34</v>
       </c>
@@ -26787,10 +26969,13 @@
         <v>20.8</v>
       </c>
       <c r="L46" t="s">
+        <v>546</v>
+      </c>
+      <c r="M46" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>34</v>
       </c>
@@ -26825,10 +27010,13 @@
         <v>21</v>
       </c>
       <c r="L47" t="s">
+        <v>546</v>
+      </c>
+      <c r="M47" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
         <v>34</v>
       </c>
@@ -26863,10 +27051,13 @@
         <v>21.3</v>
       </c>
       <c r="L48" t="s">
+        <v>546</v>
+      </c>
+      <c r="M48" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
         <v>34</v>
       </c>
@@ -26901,10 +27092,13 @@
         <v>21.5</v>
       </c>
       <c r="L49" t="s">
+        <v>546</v>
+      </c>
+      <c r="M49" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
         <v>34</v>
       </c>
@@ -26939,10 +27133,13 @@
         <v>22</v>
       </c>
       <c r="L50" t="s">
+        <v>546</v>
+      </c>
+      <c r="M50" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>34</v>
       </c>
@@ -26977,10 +27174,13 @@
         <v>22.5</v>
       </c>
       <c r="L51" t="s">
+        <v>546</v>
+      </c>
+      <c r="M51" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
         <v>34</v>
       </c>
@@ -27015,10 +27215,13 @@
         <v>23</v>
       </c>
       <c r="L52" t="s">
+        <v>546</v>
+      </c>
+      <c r="M52" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>34</v>
       </c>
@@ -27053,10 +27256,13 @@
         <v>23.5</v>
       </c>
       <c r="L53" t="s">
+        <v>546</v>
+      </c>
+      <c r="M53" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
         <v>34</v>
       </c>
@@ -27091,10 +27297,13 @@
         <v>21.5</v>
       </c>
       <c r="L54" t="s">
+        <v>544</v>
+      </c>
+      <c r="M54" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
         <v>34</v>
       </c>
@@ -27129,10 +27338,13 @@
         <v>21.8</v>
       </c>
       <c r="L55" t="s">
+        <v>544</v>
+      </c>
+      <c r="M55" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
         <v>34</v>
       </c>
@@ -27167,10 +27379,13 @@
         <v>22</v>
       </c>
       <c r="L56" t="s">
+        <v>544</v>
+      </c>
+      <c r="M56" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
         <v>34</v>
       </c>
@@ -27205,10 +27420,13 @@
         <v>22.3</v>
       </c>
       <c r="L57" t="s">
+        <v>544</v>
+      </c>
+      <c r="M57" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
         <v>34</v>
       </c>
@@ -27243,10 +27461,13 @@
         <v>22.5</v>
       </c>
       <c r="L58" t="s">
+        <v>544</v>
+      </c>
+      <c r="M58" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
         <v>34</v>
       </c>
@@ -27281,10 +27502,13 @@
         <v>22.8</v>
       </c>
       <c r="L59" t="s">
+        <v>544</v>
+      </c>
+      <c r="M59" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
         <v>34</v>
       </c>
@@ -27319,10 +27543,13 @@
         <v>23</v>
       </c>
       <c r="L60" t="s">
+        <v>544</v>
+      </c>
+      <c r="M60" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>34</v>
       </c>
@@ -27357,10 +27584,13 @@
         <v>23.3</v>
       </c>
       <c r="L61" t="s">
+        <v>544</v>
+      </c>
+      <c r="M61" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>34</v>
       </c>
@@ -27395,10 +27625,13 @@
         <v>23.5</v>
       </c>
       <c r="L62" t="s">
+        <v>544</v>
+      </c>
+      <c r="M62" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>34</v>
       </c>
@@ -27433,10 +27666,13 @@
         <v>24</v>
       </c>
       <c r="L63" t="s">
+        <v>544</v>
+      </c>
+      <c r="M63" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>34</v>
       </c>
@@ -27471,10 +27707,13 @@
         <v>24.5</v>
       </c>
       <c r="L64" t="s">
+        <v>544</v>
+      </c>
+      <c r="M64" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>34</v>
       </c>
@@ -27509,10 +27748,13 @@
         <v>25</v>
       </c>
       <c r="L65" t="s">
+        <v>544</v>
+      </c>
+      <c r="M65" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
         <v>34</v>
       </c>
@@ -27547,10 +27789,13 @@
         <v>25.5</v>
       </c>
       <c r="L66" t="s">
+        <v>544</v>
+      </c>
+      <c r="M66" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
         <v>34</v>
       </c>
@@ -27585,10 +27830,13 @@
         <v>24.75</v>
       </c>
       <c r="L67" t="s">
+        <v>544</v>
+      </c>
+      <c r="M67" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>34</v>
       </c>
@@ -27623,10 +27871,13 @@
         <v>25</v>
       </c>
       <c r="L68" t="s">
+        <v>544</v>
+      </c>
+      <c r="M68" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
         <v>34</v>
       </c>
@@ -27661,10 +27912,13 @@
         <v>25.25</v>
       </c>
       <c r="L69" t="s">
+        <v>544</v>
+      </c>
+      <c r="M69" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
         <v>34</v>
       </c>
@@ -27699,10 +27953,13 @@
         <v>25.5</v>
       </c>
       <c r="L70" t="s">
+        <v>544</v>
+      </c>
+      <c r="M70" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
         <v>34</v>
       </c>
@@ -27737,10 +27994,13 @@
         <v>25.75</v>
       </c>
       <c r="L71" t="s">
+        <v>544</v>
+      </c>
+      <c r="M71" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
         <v>34</v>
       </c>
@@ -27775,10 +28035,13 @@
         <v>26</v>
       </c>
       <c r="L72" t="s">
+        <v>544</v>
+      </c>
+      <c r="M72" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
         <v>34</v>
       </c>
@@ -27813,10 +28076,13 @@
         <v>26.25</v>
       </c>
       <c r="L73" t="s">
+        <v>544</v>
+      </c>
+      <c r="M73" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
         <v>34</v>
       </c>
@@ -27851,10 +28117,13 @@
         <v>26.5</v>
       </c>
       <c r="L74" t="s">
+        <v>544</v>
+      </c>
+      <c r="M74" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
         <v>34</v>
       </c>
@@ -27889,10 +28158,13 @@
         <v>27</v>
       </c>
       <c r="L75" t="s">
+        <v>544</v>
+      </c>
+      <c r="M75" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
         <v>34</v>
       </c>
@@ -27927,10 +28199,13 @@
         <v>27.5</v>
       </c>
       <c r="L76" t="s">
+        <v>544</v>
+      </c>
+      <c r="M76" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
         <v>34</v>
       </c>
@@ -27965,10 +28240,13 @@
         <v>28</v>
       </c>
       <c r="L77" t="s">
+        <v>544</v>
+      </c>
+      <c r="M77" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
         <v>34</v>
       </c>
@@ -28003,10 +28281,13 @@
         <v>28.5</v>
       </c>
       <c r="L78" t="s">
+        <v>544</v>
+      </c>
+      <c r="M78" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
         <v>34</v>
       </c>
@@ -28041,10 +28322,13 @@
         <v>24.5</v>
       </c>
       <c r="L79" t="s">
+        <v>544</v>
+      </c>
+      <c r="M79" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
         <v>34</v>
       </c>
@@ -28079,10 +28363,13 @@
         <v>24.75</v>
       </c>
       <c r="L80" t="s">
+        <v>544</v>
+      </c>
+      <c r="M80" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
         <v>34</v>
       </c>
@@ -28117,10 +28404,13 @@
         <v>25</v>
       </c>
       <c r="L81" t="s">
+        <v>544</v>
+      </c>
+      <c r="M81" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
         <v>34</v>
       </c>
@@ -28155,10 +28445,13 @@
         <v>25.25</v>
       </c>
       <c r="L82" t="s">
+        <v>544</v>
+      </c>
+      <c r="M82" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
         <v>34</v>
       </c>
@@ -28193,10 +28486,13 @@
         <v>25.5</v>
       </c>
       <c r="L83" t="s">
+        <v>544</v>
+      </c>
+      <c r="M83" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
         <v>34</v>
       </c>
@@ -28231,10 +28527,13 @@
         <v>25.75</v>
       </c>
       <c r="L84" t="s">
+        <v>544</v>
+      </c>
+      <c r="M84" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
         <v>34</v>
       </c>
@@ -28269,10 +28568,13 @@
         <v>26</v>
       </c>
       <c r="L85" t="s">
+        <v>544</v>
+      </c>
+      <c r="M85" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
         <v>34</v>
       </c>
@@ -28307,10 +28609,13 @@
         <v>26.25</v>
       </c>
       <c r="L86" t="s">
+        <v>544</v>
+      </c>
+      <c r="M86" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
         <v>34</v>
       </c>
@@ -28345,10 +28650,13 @@
         <v>26.5</v>
       </c>
       <c r="L87" t="s">
+        <v>544</v>
+      </c>
+      <c r="M87" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
         <v>34</v>
       </c>
@@ -28383,10 +28691,13 @@
         <v>27</v>
       </c>
       <c r="L88" t="s">
+        <v>544</v>
+      </c>
+      <c r="M88" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
         <v>34</v>
       </c>
@@ -28421,10 +28732,13 @@
         <v>27.5</v>
       </c>
       <c r="L89" t="s">
+        <v>544</v>
+      </c>
+      <c r="M89" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
         <v>34</v>
       </c>
@@ -28459,10 +28773,13 @@
         <v>28</v>
       </c>
       <c r="L90" t="s">
+        <v>544</v>
+      </c>
+      <c r="M90" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
         <v>34</v>
       </c>
@@ -28497,10 +28814,13 @@
         <v>28.5</v>
       </c>
       <c r="L91" t="s">
+        <v>544</v>
+      </c>
+      <c r="M91" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
         <v>34</v>
       </c>
@@ -28535,10 +28855,13 @@
         <v>19.899999999999999</v>
       </c>
       <c r="L92" t="s">
+        <v>544</v>
+      </c>
+      <c r="M92" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
         <v>34</v>
       </c>
@@ -28573,10 +28896,13 @@
         <v>20.25</v>
       </c>
       <c r="L93" t="s">
+        <v>544</v>
+      </c>
+      <c r="M93" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
         <v>34</v>
       </c>
@@ -28611,10 +28937,13 @@
         <v>20.6</v>
       </c>
       <c r="L94" t="s">
+        <v>544</v>
+      </c>
+      <c r="M94" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
         <v>34</v>
       </c>
@@ -28649,10 +28978,13 @@
         <v>20.95</v>
       </c>
       <c r="L95" t="s">
+        <v>544</v>
+      </c>
+      <c r="M95" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
         <v>34</v>
       </c>
@@ -28687,10 +29019,13 @@
         <v>21.3</v>
       </c>
       <c r="L96" t="s">
+        <v>544</v>
+      </c>
+      <c r="M96" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
         <v>34</v>
       </c>
@@ -28725,10 +29060,13 @@
         <v>21.65</v>
       </c>
       <c r="L97" t="s">
+        <v>544</v>
+      </c>
+      <c r="M97" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
         <v>34</v>
       </c>
@@ -28763,10 +29101,13 @@
         <v>22</v>
       </c>
       <c r="L98" t="s">
+        <v>544</v>
+      </c>
+      <c r="M98" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
         <v>34</v>
       </c>
@@ -28801,10 +29142,13 @@
         <v>22.35</v>
       </c>
       <c r="L99" t="s">
+        <v>544</v>
+      </c>
+      <c r="M99" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
         <v>34</v>
       </c>
@@ -28839,10 +29183,13 @@
         <v>22.7</v>
       </c>
       <c r="L100" t="s">
+        <v>544</v>
+      </c>
+      <c r="M100" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
         <v>34</v>
       </c>
@@ -28877,10 +29224,13 @@
         <v>23.4</v>
       </c>
       <c r="L101" t="s">
+        <v>544</v>
+      </c>
+      <c r="M101" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
         <v>34</v>
       </c>
@@ -28915,10 +29265,13 @@
         <v>24.1</v>
       </c>
       <c r="L102" t="s">
+        <v>544</v>
+      </c>
+      <c r="M102" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
         <v>34</v>
       </c>
@@ -28953,10 +29306,13 @@
         <v>24.8</v>
       </c>
       <c r="L103" t="s">
+        <v>544</v>
+      </c>
+      <c r="M103" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
         <v>34</v>
       </c>
@@ -28991,10 +29347,13 @@
         <v>25.5</v>
       </c>
       <c r="L104" t="s">
+        <v>544</v>
+      </c>
+      <c r="M104" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
         <v>34</v>
       </c>
@@ -29029,10 +29388,13 @@
         <v>24</v>
       </c>
       <c r="L105" t="s">
+        <v>544</v>
+      </c>
+      <c r="M105" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
         <v>34</v>
       </c>
@@ -29067,10 +29429,13 @@
         <v>24.3</v>
       </c>
       <c r="L106" t="s">
+        <v>544</v>
+      </c>
+      <c r="M106" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
         <v>34</v>
       </c>
@@ -29105,10 +29470,13 @@
         <v>24.5</v>
       </c>
       <c r="L107" t="s">
+        <v>544</v>
+      </c>
+      <c r="M107" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
         <v>34</v>
       </c>
@@ -29143,10 +29511,13 @@
         <v>24.8</v>
       </c>
       <c r="L108" t="s">
+        <v>544</v>
+      </c>
+      <c r="M108" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
         <v>34</v>
       </c>
@@ -29181,10 +29552,13 @@
         <v>25</v>
       </c>
       <c r="L109" t="s">
+        <v>544</v>
+      </c>
+      <c r="M109" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
         <v>34</v>
       </c>
@@ -29219,10 +29593,13 @@
         <v>25.3</v>
       </c>
       <c r="L110" t="s">
+        <v>544</v>
+      </c>
+      <c r="M110" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
         <v>34</v>
       </c>
@@ -29257,10 +29634,13 @@
         <v>25.5</v>
       </c>
       <c r="L111" t="s">
+        <v>544</v>
+      </c>
+      <c r="M111" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
         <v>34</v>
       </c>
@@ -29295,10 +29675,13 @@
         <v>25.8</v>
       </c>
       <c r="L112" t="s">
+        <v>544</v>
+      </c>
+      <c r="M112" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
         <v>34</v>
       </c>
@@ -29333,10 +29716,13 @@
         <v>26</v>
       </c>
       <c r="L113" t="s">
+        <v>544</v>
+      </c>
+      <c r="M113" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
         <v>34</v>
       </c>
@@ -29371,10 +29757,13 @@
         <v>26.5</v>
       </c>
       <c r="L114" t="s">
+        <v>544</v>
+      </c>
+      <c r="M114" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
         <v>34</v>
       </c>
@@ -29409,10 +29798,13 @@
         <v>27</v>
       </c>
       <c r="L115" t="s">
+        <v>544</v>
+      </c>
+      <c r="M115" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
         <v>34</v>
       </c>
@@ -29447,10 +29839,13 @@
         <v>27.5</v>
       </c>
       <c r="L116" t="s">
+        <v>544</v>
+      </c>
+      <c r="M116" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
         <v>34</v>
       </c>
@@ -29485,10 +29880,13 @@
         <v>24.75</v>
       </c>
       <c r="L117" t="s">
+        <v>547</v>
+      </c>
+      <c r="M117" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
         <v>34</v>
       </c>
@@ -29523,10 +29921,13 @@
         <v>25.75</v>
       </c>
       <c r="L118" t="s">
+        <v>547</v>
+      </c>
+      <c r="M118" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
         <v>34</v>
       </c>
@@ -29561,10 +29962,13 @@
         <v>26.75</v>
       </c>
       <c r="L119" t="s">
+        <v>547</v>
+      </c>
+      <c r="M119" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
         <v>34</v>
       </c>
@@ -29599,10 +30003,13 @@
         <v>27.75</v>
       </c>
       <c r="L120" t="s">
+        <v>547</v>
+      </c>
+      <c r="M120" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
         <v>34</v>
       </c>
@@ -29637,10 +30044,13 @@
         <v>24</v>
       </c>
       <c r="L121" t="s">
+        <v>544</v>
+      </c>
+      <c r="M121" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
         <v>34</v>
       </c>
@@ -29675,10 +30085,13 @@
         <v>24.3</v>
       </c>
       <c r="L122" t="s">
+        <v>544</v>
+      </c>
+      <c r="M122" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
         <v>34</v>
       </c>
@@ -29713,10 +30126,13 @@
         <v>24.5</v>
       </c>
       <c r="L123" t="s">
+        <v>544</v>
+      </c>
+      <c r="M123" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
         <v>34</v>
       </c>
@@ -29751,10 +30167,13 @@
         <v>24.8</v>
       </c>
       <c r="L124" t="s">
+        <v>544</v>
+      </c>
+      <c r="M124" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
         <v>34</v>
       </c>
@@ -29789,10 +30208,13 @@
         <v>25</v>
       </c>
       <c r="L125" t="s">
+        <v>544</v>
+      </c>
+      <c r="M125" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
         <v>34</v>
       </c>
@@ -29827,10 +30249,13 @@
         <v>25.3</v>
       </c>
       <c r="L126" t="s">
+        <v>544</v>
+      </c>
+      <c r="M126" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
         <v>34</v>
       </c>
@@ -29865,10 +30290,13 @@
         <v>25.5</v>
       </c>
       <c r="L127" t="s">
+        <v>544</v>
+      </c>
+      <c r="M127" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
         <v>34</v>
       </c>
@@ -29903,10 +30331,13 @@
         <v>25.5</v>
       </c>
       <c r="L128" t="s">
+        <v>546</v>
+      </c>
+      <c r="M128" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
         <v>34</v>
       </c>
@@ -29941,10 +30372,13 @@
         <v>25.75</v>
       </c>
       <c r="L129" t="s">
+        <v>546</v>
+      </c>
+      <c r="M129" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
         <v>34</v>
       </c>
@@ -29979,10 +30413,13 @@
         <v>26</v>
       </c>
       <c r="L130" t="s">
+        <v>546</v>
+      </c>
+      <c r="M130" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
         <v>34</v>
       </c>
@@ -30017,10 +30454,13 @@
         <v>26.25</v>
       </c>
       <c r="L131" t="s">
+        <v>546</v>
+      </c>
+      <c r="M131" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
         <v>34</v>
       </c>
@@ -30055,10 +30495,13 @@
         <v>26.5</v>
       </c>
       <c r="L132" t="s">
+        <v>546</v>
+      </c>
+      <c r="M132" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
         <v>34</v>
       </c>
@@ -30093,10 +30536,13 @@
         <v>26.75</v>
       </c>
       <c r="L133" t="s">
+        <v>546</v>
+      </c>
+      <c r="M133" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
         <v>34</v>
       </c>
@@ -30131,10 +30577,13 @@
         <v>27</v>
       </c>
       <c r="L134" t="s">
+        <v>546</v>
+      </c>
+      <c r="M134" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
         <v>34</v>
       </c>
@@ -30169,10 +30618,13 @@
         <v>27.25</v>
       </c>
       <c r="L135" t="s">
+        <v>546</v>
+      </c>
+      <c r="M135" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
         <v>34</v>
       </c>
@@ -30207,10 +30659,13 @@
         <v>27.5</v>
       </c>
       <c r="L136" t="s">
+        <v>546</v>
+      </c>
+      <c r="M136" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
         <v>34</v>
       </c>
@@ -30245,10 +30700,13 @@
         <v>28</v>
       </c>
       <c r="L137" t="s">
+        <v>546</v>
+      </c>
+      <c r="M137" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
         <v>34</v>
       </c>
@@ -30283,10 +30741,13 @@
         <v>26.25</v>
       </c>
       <c r="L138" t="s">
+        <v>546</v>
+      </c>
+      <c r="M138" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
         <v>34</v>
       </c>
@@ -30321,10 +30782,13 @@
         <v>26.5</v>
       </c>
       <c r="L139" t="s">
+        <v>546</v>
+      </c>
+      <c r="M139" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
         <v>34</v>
       </c>
@@ -30359,10 +30823,13 @@
         <v>26.75</v>
       </c>
       <c r="L140" t="s">
+        <v>546</v>
+      </c>
+      <c r="M140" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
         <v>34</v>
       </c>
@@ -30397,10 +30864,13 @@
         <v>27</v>
       </c>
       <c r="L141" t="s">
+        <v>546</v>
+      </c>
+      <c r="M141" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
         <v>34</v>
       </c>
@@ -30435,10 +30905,13 @@
         <v>27.25</v>
       </c>
       <c r="L142" t="s">
+        <v>546</v>
+      </c>
+      <c r="M142" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
         <v>34</v>
       </c>
@@ -30473,10 +30946,13 @@
         <v>27.5</v>
       </c>
       <c r="L143" t="s">
+        <v>546</v>
+      </c>
+      <c r="M143" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
         <v>34</v>
       </c>
@@ -30511,10 +30987,13 @@
         <v>27.75</v>
       </c>
       <c r="L144" t="s">
+        <v>546</v>
+      </c>
+      <c r="M144" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
         <v>34</v>
       </c>
@@ -30549,10 +31028,13 @@
         <v>28.75</v>
       </c>
       <c r="L145" t="s">
+        <v>546</v>
+      </c>
+      <c r="M145" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
         <v>34</v>
       </c>
@@ -30587,10 +31069,13 @@
         <v>23</v>
       </c>
       <c r="L146" t="s">
+        <v>546</v>
+      </c>
+      <c r="M146" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
         <v>34</v>
       </c>
@@ -30625,10 +31110,13 @@
         <v>23.25</v>
       </c>
       <c r="L147" t="s">
+        <v>546</v>
+      </c>
+      <c r="M147" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
         <v>34</v>
       </c>
@@ -30663,10 +31151,13 @@
         <v>23.5</v>
       </c>
       <c r="L148" t="s">
+        <v>546</v>
+      </c>
+      <c r="M148" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
         <v>34</v>
       </c>
@@ -30701,10 +31192,13 @@
         <v>23.75</v>
       </c>
       <c r="L149" t="s">
+        <v>546</v>
+      </c>
+      <c r="M149" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
         <v>34</v>
       </c>
@@ -30739,10 +31233,13 @@
         <v>24</v>
       </c>
       <c r="L150" t="s">
+        <v>546</v>
+      </c>
+      <c r="M150" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
         <v>34</v>
       </c>
@@ -30777,10 +31274,13 @@
         <v>24.25</v>
       </c>
       <c r="L151" t="s">
+        <v>546</v>
+      </c>
+      <c r="M151" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
         <v>34</v>
       </c>
@@ -30815,10 +31315,13 @@
         <v>24.5</v>
       </c>
       <c r="L152" t="s">
+        <v>546</v>
+      </c>
+      <c r="M152" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
         <v>34</v>
       </c>
@@ -30853,10 +31356,13 @@
         <v>24.75</v>
       </c>
       <c r="L153" t="s">
+        <v>546</v>
+      </c>
+      <c r="M153" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
         <v>34</v>
       </c>
@@ -30891,10 +31397,13 @@
         <v>25</v>
       </c>
       <c r="L154" t="s">
+        <v>546</v>
+      </c>
+      <c r="M154" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
         <v>34</v>
       </c>
@@ -30929,10 +31438,13 @@
         <v>25.5</v>
       </c>
       <c r="L155" t="s">
+        <v>546</v>
+      </c>
+      <c r="M155" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
         <v>34</v>
       </c>
@@ -30967,10 +31479,13 @@
         <v>27</v>
       </c>
       <c r="L156" t="s">
+        <v>544</v>
+      </c>
+      <c r="M156" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
         <v>34</v>
       </c>
@@ -31005,10 +31520,13 @@
         <v>27.25</v>
       </c>
       <c r="L157" t="s">
+        <v>544</v>
+      </c>
+      <c r="M157" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
         <v>34</v>
       </c>
@@ -31043,10 +31561,13 @@
         <v>27.5</v>
       </c>
       <c r="L158" t="s">
+        <v>544</v>
+      </c>
+      <c r="M158" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
         <v>34</v>
       </c>
@@ -31081,10 +31602,13 @@
         <v>27.75</v>
       </c>
       <c r="L159" t="s">
+        <v>544</v>
+      </c>
+      <c r="M159" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
         <v>34</v>
       </c>
@@ -31119,10 +31643,13 @@
         <v>28</v>
       </c>
       <c r="L160" t="s">
+        <v>544</v>
+      </c>
+      <c r="M160" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
         <v>34</v>
       </c>
@@ -31157,10 +31684,13 @@
         <v>28.25</v>
       </c>
       <c r="L161" t="s">
+        <v>544</v>
+      </c>
+      <c r="M161" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
         <v>34</v>
       </c>
@@ -31195,10 +31725,13 @@
         <v>28.5</v>
       </c>
       <c r="L162" t="s">
+        <v>544</v>
+      </c>
+      <c r="M162" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
         <v>34</v>
       </c>
@@ -31233,10 +31766,13 @@
         <v>17</v>
       </c>
       <c r="L163" t="s">
+        <v>546</v>
+      </c>
+      <c r="M163" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
         <v>34</v>
       </c>
@@ -31271,10 +31807,13 @@
         <v>17.25</v>
       </c>
       <c r="L164" t="s">
+        <v>546</v>
+      </c>
+      <c r="M164" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
         <v>34</v>
       </c>
@@ -31309,10 +31848,13 @@
         <v>17.5</v>
       </c>
       <c r="L165" t="s">
+        <v>546</v>
+      </c>
+      <c r="M165" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
         <v>34</v>
       </c>
@@ -31347,10 +31889,13 @@
         <v>17.75</v>
       </c>
       <c r="L166" t="s">
+        <v>546</v>
+      </c>
+      <c r="M166" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
         <v>34</v>
       </c>
@@ -31385,10 +31930,13 @@
         <v>18</v>
       </c>
       <c r="L167" t="s">
+        <v>546</v>
+      </c>
+      <c r="M167" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
         <v>34</v>
       </c>
@@ -31423,10 +31971,13 @@
         <v>18.25</v>
       </c>
       <c r="L168" t="s">
+        <v>546</v>
+      </c>
+      <c r="M168" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
         <v>34</v>
       </c>
@@ -31461,10 +32012,13 @@
         <v>18.5</v>
       </c>
       <c r="L169" t="s">
+        <v>546</v>
+      </c>
+      <c r="M169" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
         <v>34</v>
       </c>
@@ -31499,10 +32053,13 @@
         <v>18.75</v>
       </c>
       <c r="L170" t="s">
+        <v>546</v>
+      </c>
+      <c r="M170" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
         <v>34</v>
       </c>
@@ -31537,10 +32094,13 @@
         <v>19</v>
       </c>
       <c r="L171" t="s">
+        <v>546</v>
+      </c>
+      <c r="M171" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
         <v>34</v>
       </c>
@@ -31575,10 +32135,13 @@
         <v>19.5</v>
       </c>
       <c r="L172" t="s">
+        <v>546</v>
+      </c>
+      <c r="M172" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
         <v>34</v>
       </c>
@@ -31613,10 +32176,13 @@
         <v>22.5</v>
       </c>
       <c r="L173" t="s">
+        <v>547</v>
+      </c>
+      <c r="M173" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
         <v>34</v>
       </c>
@@ -31651,10 +32217,13 @@
         <v>23</v>
       </c>
       <c r="L174" t="s">
+        <v>547</v>
+      </c>
+      <c r="M174" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
         <v>34</v>
       </c>
@@ -31689,10 +32258,13 @@
         <v>23.5</v>
       </c>
       <c r="L175" t="s">
+        <v>547</v>
+      </c>
+      <c r="M175" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
         <v>34</v>
       </c>
@@ -31727,10 +32299,13 @@
         <v>24</v>
       </c>
       <c r="L176" t="s">
+        <v>547</v>
+      </c>
+      <c r="M176" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
         <v>34</v>
       </c>
@@ -31765,10 +32340,13 @@
         <v>25.25</v>
       </c>
       <c r="L177" t="s">
+        <v>544</v>
+      </c>
+      <c r="M177" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
         <v>34</v>
       </c>
@@ -31803,10 +32381,13 @@
         <v>25.5</v>
       </c>
       <c r="L178" t="s">
+        <v>544</v>
+      </c>
+      <c r="M178" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
         <v>34</v>
       </c>
@@ -31841,10 +32422,13 @@
         <v>25.75</v>
       </c>
       <c r="L179" t="s">
+        <v>544</v>
+      </c>
+      <c r="M179" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
         <v>34</v>
       </c>
@@ -31879,10 +32463,13 @@
         <v>26</v>
       </c>
       <c r="L180" t="s">
+        <v>544</v>
+      </c>
+      <c r="M180" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
         <v>34</v>
       </c>
@@ -31917,10 +32504,13 @@
         <v>26.25</v>
       </c>
       <c r="L181" t="s">
+        <v>544</v>
+      </c>
+      <c r="M181" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
         <v>34</v>
       </c>
@@ -31955,10 +32545,13 @@
         <v>26.5</v>
       </c>
       <c r="L182" t="s">
+        <v>544</v>
+      </c>
+      <c r="M182" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
         <v>34</v>
       </c>
@@ -31993,10 +32586,13 @@
         <v>26.75</v>
       </c>
       <c r="L183" t="s">
+        <v>544</v>
+      </c>
+      <c r="M183" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
         <v>34</v>
       </c>
@@ -32031,10 +32627,13 @@
         <v>27</v>
       </c>
       <c r="L184" t="s">
+        <v>544</v>
+      </c>
+      <c r="M184" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
         <v>34</v>
       </c>
@@ -32069,10 +32668,13 @@
         <v>27.25</v>
       </c>
       <c r="L185" t="s">
+        <v>544</v>
+      </c>
+      <c r="M185" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
         <v>34</v>
       </c>
@@ -32107,10 +32709,13 @@
         <v>21.25</v>
       </c>
       <c r="L186" t="s">
+        <v>544</v>
+      </c>
+      <c r="M186" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
         <v>34</v>
       </c>
@@ -32145,10 +32750,13 @@
         <v>21.5</v>
       </c>
       <c r="L187" t="s">
+        <v>544</v>
+      </c>
+      <c r="M187" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
         <v>34</v>
       </c>
@@ -32183,10 +32791,13 @@
         <v>21.75</v>
       </c>
       <c r="L188" t="s">
+        <v>544</v>
+      </c>
+      <c r="M188" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
         <v>34</v>
       </c>
@@ -32221,10 +32832,13 @@
         <v>22</v>
       </c>
       <c r="L189" t="s">
+        <v>544</v>
+      </c>
+      <c r="M189" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
         <v>34</v>
       </c>
@@ -32259,10 +32873,13 @@
         <v>22.25</v>
       </c>
       <c r="L190" t="s">
+        <v>544</v>
+      </c>
+      <c r="M190" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
         <v>34</v>
       </c>
@@ -32297,10 +32914,13 @@
         <v>22.5</v>
       </c>
       <c r="L191" t="s">
+        <v>544</v>
+      </c>
+      <c r="M191" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
         <v>34</v>
       </c>
@@ -32335,10 +32955,13 @@
         <v>22.75</v>
       </c>
       <c r="L192" t="s">
+        <v>544</v>
+      </c>
+      <c r="M192" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
         <v>34</v>
       </c>
@@ -32373,10 +32996,13 @@
         <v>23</v>
       </c>
       <c r="L193" t="s">
+        <v>544</v>
+      </c>
+      <c r="M193" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
         <v>34</v>
       </c>
@@ -32411,10 +33037,13 @@
         <v>23.5</v>
       </c>
       <c r="L194" t="s">
+        <v>544</v>
+      </c>
+      <c r="M194" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
         <v>10</v>
       </c>
@@ -32449,10 +33078,13 @@
         <v>18.5</v>
       </c>
       <c r="L195" t="s">
+        <v>544</v>
+      </c>
+      <c r="M195" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
         <v>10</v>
       </c>
@@ -32487,10 +33119,13 @@
         <v>18.5</v>
       </c>
       <c r="L196" t="s">
+        <v>544</v>
+      </c>
+      <c r="M196" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
         <v>10</v>
       </c>
@@ -32525,10 +33160,13 @@
         <v>19</v>
       </c>
       <c r="L197" t="s">
+        <v>544</v>
+      </c>
+      <c r="M197" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
         <v>10</v>
       </c>
@@ -32563,10 +33201,13 @@
         <v>19.5</v>
       </c>
       <c r="L198" t="s">
+        <v>544</v>
+      </c>
+      <c r="M198" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
         <v>10</v>
       </c>
@@ -32601,10 +33242,13 @@
         <v>20</v>
       </c>
       <c r="L199" t="s">
+        <v>544</v>
+      </c>
+      <c r="M199" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
         <v>10</v>
       </c>
@@ -32639,10 +33283,13 @@
         <v>20.5</v>
       </c>
       <c r="L200" t="s">
+        <v>544</v>
+      </c>
+      <c r="M200" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
         <v>10</v>
       </c>
@@ -32677,10 +33324,13 @@
         <v>20.5</v>
       </c>
       <c r="L201" t="s">
+        <v>544</v>
+      </c>
+      <c r="M201" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
         <v>10</v>
       </c>
@@ -32715,10 +33365,13 @@
         <v>21</v>
       </c>
       <c r="L202" t="s">
+        <v>544</v>
+      </c>
+      <c r="M202" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
         <v>10</v>
       </c>
@@ -32753,10 +33406,13 @@
         <v>21.5</v>
       </c>
       <c r="L203" t="s">
+        <v>544</v>
+      </c>
+      <c r="M203" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A204" t="s">
         <v>10</v>
       </c>
@@ -32791,10 +33447,13 @@
         <v>21.5</v>
       </c>
       <c r="L204" t="s">
+        <v>544</v>
+      </c>
+      <c r="M204" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
         <v>10</v>
       </c>
@@ -32829,10 +33488,13 @@
         <v>18.5</v>
       </c>
       <c r="L205" t="s">
+        <v>544</v>
+      </c>
+      <c r="M205" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
         <v>10</v>
       </c>
@@ -32867,10 +33529,13 @@
         <v>18.5</v>
       </c>
       <c r="L206" t="s">
+        <v>544</v>
+      </c>
+      <c r="M206" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A207" t="s">
         <v>10</v>
       </c>
@@ -32905,10 +33570,13 @@
         <v>19</v>
       </c>
       <c r="L207" t="s">
+        <v>544</v>
+      </c>
+      <c r="M207" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
         <v>10</v>
       </c>
@@ -32943,10 +33611,13 @@
         <v>19.5</v>
       </c>
       <c r="L208" t="s">
+        <v>544</v>
+      </c>
+      <c r="M208" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
         <v>10</v>
       </c>
@@ -32981,10 +33652,13 @@
         <v>20</v>
       </c>
       <c r="L209" t="s">
+        <v>544</v>
+      </c>
+      <c r="M209" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
         <v>10</v>
       </c>
@@ -33019,10 +33693,13 @@
         <v>20.5</v>
       </c>
       <c r="L210" t="s">
+        <v>544</v>
+      </c>
+      <c r="M210" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
         <v>10</v>
       </c>
@@ -33057,10 +33734,13 @@
         <v>20.5</v>
       </c>
       <c r="L211" t="s">
+        <v>544</v>
+      </c>
+      <c r="M211" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
         <v>10</v>
       </c>
@@ -33095,10 +33775,13 @@
         <v>21</v>
       </c>
       <c r="L212" t="s">
+        <v>544</v>
+      </c>
+      <c r="M212" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
         <v>10</v>
       </c>
@@ -33133,10 +33816,13 @@
         <v>21.5</v>
       </c>
       <c r="L213" t="s">
+        <v>544</v>
+      </c>
+      <c r="M213" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
         <v>10</v>
       </c>
@@ -33171,10 +33857,13 @@
         <v>21.5</v>
       </c>
       <c r="L214" t="s">
+        <v>544</v>
+      </c>
+      <c r="M214" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
         <v>10</v>
       </c>
@@ -33209,10 +33898,13 @@
         <v>22</v>
       </c>
       <c r="L215" t="s">
+        <v>544</v>
+      </c>
+      <c r="M215" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
         <v>10</v>
       </c>
@@ -33247,10 +33939,13 @@
         <v>22.5</v>
       </c>
       <c r="L216" t="s">
+        <v>544</v>
+      </c>
+      <c r="M216" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
         <v>10</v>
       </c>
@@ -33285,10 +33980,13 @@
         <v>23</v>
       </c>
       <c r="L217" t="s">
+        <v>544</v>
+      </c>
+      <c r="M217" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
         <v>10</v>
       </c>
@@ -33323,10 +34021,13 @@
         <v>23.5</v>
       </c>
       <c r="L218" t="s">
+        <v>544</v>
+      </c>
+      <c r="M218" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
         <v>10</v>
       </c>
@@ -33361,10 +34062,13 @@
         <v>24</v>
       </c>
       <c r="L219" t="s">
+        <v>544</v>
+      </c>
+      <c r="M219" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
         <v>10</v>
       </c>
@@ -33399,10 +34103,13 @@
         <v>24.5</v>
       </c>
       <c r="L220" t="s">
+        <v>544</v>
+      </c>
+      <c r="M220" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
         <v>10</v>
       </c>
@@ -33437,10 +34144,13 @@
         <v>24.5</v>
       </c>
       <c r="L221" t="s">
+        <v>544</v>
+      </c>
+      <c r="M221" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
         <v>10</v>
       </c>
@@ -33475,10 +34185,13 @@
         <v>25</v>
       </c>
       <c r="L222" t="s">
+        <v>544</v>
+      </c>
+      <c r="M222" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
         <v>10</v>
       </c>
@@ -33513,10 +34226,13 @@
         <v>25.5</v>
       </c>
       <c r="L223" t="s">
+        <v>544</v>
+      </c>
+      <c r="M223" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
         <v>10</v>
       </c>
@@ -33551,10 +34267,13 @@
         <v>25.5</v>
       </c>
       <c r="L224" t="s">
+        <v>544</v>
+      </c>
+      <c r="M224" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
         <v>10</v>
       </c>
@@ -33589,10 +34308,13 @@
         <v>22</v>
       </c>
       <c r="L225" t="s">
+        <v>544</v>
+      </c>
+      <c r="M225" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
         <v>10</v>
       </c>
@@ -33627,10 +34349,13 @@
         <v>22.5</v>
       </c>
       <c r="L226" t="s">
+        <v>544</v>
+      </c>
+      <c r="M226" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
         <v>10</v>
       </c>
@@ -33665,10 +34390,13 @@
         <v>22.5</v>
       </c>
       <c r="L227" t="s">
+        <v>544</v>
+      </c>
+      <c r="M227" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
         <v>10</v>
       </c>
@@ -33703,10 +34431,13 @@
         <v>23</v>
       </c>
       <c r="L228" t="s">
+        <v>544</v>
+      </c>
+      <c r="M228" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
         <v>10</v>
       </c>
@@ -33741,10 +34472,13 @@
         <v>23.5</v>
       </c>
       <c r="L229" t="s">
+        <v>544</v>
+      </c>
+      <c r="M229" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
         <v>10</v>
       </c>
@@ -33779,10 +34513,13 @@
         <v>24</v>
       </c>
       <c r="L230" t="s">
+        <v>544</v>
+      </c>
+      <c r="M230" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
         <v>10</v>
       </c>
@@ -33817,10 +34554,13 @@
         <v>24</v>
       </c>
       <c r="L231" t="s">
+        <v>544</v>
+      </c>
+      <c r="M231" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
         <v>10</v>
       </c>
@@ -33855,10 +34595,13 @@
         <v>24.5</v>
       </c>
       <c r="L232" t="s">
+        <v>544</v>
+      </c>
+      <c r="M232" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
         <v>10</v>
       </c>
@@ -33893,10 +34636,13 @@
         <v>24.5</v>
       </c>
       <c r="L233" t="s">
+        <v>544</v>
+      </c>
+      <c r="M233" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
         <v>10</v>
       </c>
@@ -33931,10 +34677,13 @@
         <v>25</v>
       </c>
       <c r="L234" t="s">
+        <v>544</v>
+      </c>
+      <c r="M234" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
         <v>10</v>
       </c>
@@ -33969,10 +34718,13 @@
         <v>25.5</v>
       </c>
       <c r="L235" t="s">
+        <v>544</v>
+      </c>
+      <c r="M235" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
         <v>10</v>
       </c>
@@ -34007,10 +34759,13 @@
         <v>25.5</v>
       </c>
       <c r="L236" t="s">
+        <v>544</v>
+      </c>
+      <c r="M236" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
         <v>10</v>
       </c>
@@ -34045,10 +34800,13 @@
         <v>22.5</v>
       </c>
       <c r="L237" t="s">
+        <v>547</v>
+      </c>
+      <c r="M237" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
         <v>10</v>
       </c>
@@ -34083,10 +34841,13 @@
         <v>23.5</v>
       </c>
       <c r="L238" t="s">
+        <v>547</v>
+      </c>
+      <c r="M238" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
         <v>10</v>
       </c>
@@ -34121,10 +34882,13 @@
         <v>24.5</v>
       </c>
       <c r="L239" t="s">
+        <v>547</v>
+      </c>
+      <c r="M239" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A240" t="s">
         <v>10</v>
       </c>
@@ -34159,10 +34923,13 @@
         <v>25</v>
       </c>
       <c r="L240" t="s">
+        <v>547</v>
+      </c>
+      <c r="M240" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
         <v>10</v>
       </c>
@@ -34197,10 +34964,13 @@
         <v>26</v>
       </c>
       <c r="L241" t="s">
+        <v>547</v>
+      </c>
+      <c r="M241" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
         <v>10</v>
       </c>
@@ -34235,10 +35005,13 @@
         <v>26.5</v>
       </c>
       <c r="L242" t="s">
+        <v>547</v>
+      </c>
+      <c r="M242" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A243" t="s">
         <v>10</v>
       </c>
@@ -34273,10 +35046,13 @@
         <v>27.5</v>
       </c>
       <c r="L243" t="s">
+        <v>547</v>
+      </c>
+      <c r="M243" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
         <v>10</v>
       </c>
@@ -34311,10 +35087,13 @@
         <v>28.5</v>
       </c>
       <c r="L244" t="s">
+        <v>547</v>
+      </c>
+      <c r="M244" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
         <v>10</v>
       </c>
@@ -34349,10 +35128,13 @@
         <v>23</v>
       </c>
       <c r="L245" t="s">
+        <v>544</v>
+      </c>
+      <c r="M245" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
         <v>10</v>
       </c>
@@ -34387,10 +35169,13 @@
         <v>24</v>
       </c>
       <c r="L246" t="s">
+        <v>544</v>
+      </c>
+      <c r="M246" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
         <v>10</v>
       </c>
@@ -34425,10 +35210,13 @@
         <v>24.5</v>
       </c>
       <c r="L247" t="s">
+        <v>544</v>
+      </c>
+      <c r="M247" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
         <v>10</v>
       </c>
@@ -34463,10 +35251,13 @@
         <v>25</v>
       </c>
       <c r="L248" t="s">
+        <v>544</v>
+      </c>
+      <c r="M248" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
         <v>10</v>
       </c>
@@ -34501,10 +35292,13 @@
         <v>25.5</v>
       </c>
       <c r="L249" t="s">
+        <v>544</v>
+      </c>
+      <c r="M249" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A250" t="s">
         <v>10</v>
       </c>
@@ -34539,10 +35333,13 @@
         <v>26</v>
       </c>
       <c r="L250" t="s">
+        <v>544</v>
+      </c>
+      <c r="M250" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
         <v>10</v>
       </c>
@@ -34577,10 +35374,13 @@
         <v>26.5</v>
       </c>
       <c r="L251" t="s">
+        <v>544</v>
+      </c>
+      <c r="M251" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
         <v>10</v>
       </c>
@@ -34615,10 +35415,13 @@
         <v>23</v>
       </c>
       <c r="L252" t="s">
+        <v>544</v>
+      </c>
+      <c r="M252" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
         <v>10</v>
       </c>
@@ -34653,10 +35456,13 @@
         <v>24</v>
       </c>
       <c r="L253" t="s">
+        <v>544</v>
+      </c>
+      <c r="M253" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A254" t="s">
         <v>10</v>
       </c>
@@ -34691,10 +35497,13 @@
         <v>24.5</v>
       </c>
       <c r="L254" t="s">
+        <v>544</v>
+      </c>
+      <c r="M254" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
         <v>10</v>
       </c>
@@ -34729,10 +35538,13 @@
         <v>25</v>
       </c>
       <c r="L255" t="s">
+        <v>544</v>
+      </c>
+      <c r="M255" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
         <v>10</v>
       </c>
@@ -34767,10 +35579,13 @@
         <v>25.5</v>
       </c>
       <c r="L256" t="s">
+        <v>544</v>
+      </c>
+      <c r="M256" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
         <v>10</v>
       </c>
@@ -34805,10 +35620,13 @@
         <v>26</v>
       </c>
       <c r="L257" t="s">
+        <v>544</v>
+      </c>
+      <c r="M257" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A258" t="s">
         <v>10</v>
       </c>
@@ -34843,10 +35661,13 @@
         <v>26.5</v>
       </c>
       <c r="L258" t="s">
+        <v>544</v>
+      </c>
+      <c r="M258" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
         <v>10</v>
       </c>
@@ -34881,10 +35702,13 @@
         <v>26.5</v>
       </c>
       <c r="L259" t="s">
+        <v>547</v>
+      </c>
+      <c r="M259" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
         <v>10</v>
       </c>
@@ -34919,10 +35743,13 @@
         <v>27.5</v>
       </c>
       <c r="L260" t="s">
+        <v>547</v>
+      </c>
+      <c r="M260" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
         <v>10</v>
       </c>
@@ -34957,10 +35784,13 @@
         <v>28</v>
       </c>
       <c r="L261" t="s">
+        <v>547</v>
+      </c>
+      <c r="M261" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A262" t="s">
         <v>10</v>
       </c>
@@ -34995,10 +35825,13 @@
         <v>28.5</v>
       </c>
       <c r="L262" t="s">
+        <v>547</v>
+      </c>
+      <c r="M262" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
         <v>10</v>
       </c>
@@ -35033,10 +35866,13 @@
         <v>29.5</v>
       </c>
       <c r="L263" t="s">
+        <v>547</v>
+      </c>
+      <c r="M263" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
         <v>10</v>
       </c>
@@ -35071,10 +35907,13 @@
         <v>30</v>
       </c>
       <c r="L264" t="s">
+        <v>547</v>
+      </c>
+      <c r="M264" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
         <v>10</v>
       </c>
@@ -35109,10 +35948,13 @@
         <v>31</v>
       </c>
       <c r="L265" t="s">
+        <v>547</v>
+      </c>
+      <c r="M265" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
         <v>10</v>
       </c>
@@ -35147,10 +35989,13 @@
         <v>25</v>
       </c>
       <c r="L266" t="s">
+        <v>547</v>
+      </c>
+      <c r="M266" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
         <v>10</v>
       </c>
@@ -35185,10 +36030,13 @@
         <v>26</v>
       </c>
       <c r="L267" t="s">
+        <v>547</v>
+      </c>
+      <c r="M267" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A268" t="s">
         <v>10</v>
       </c>
@@ -35223,10 +36071,13 @@
         <v>27</v>
       </c>
       <c r="L268" t="s">
+        <v>547</v>
+      </c>
+      <c r="M268" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A269" t="s">
         <v>10</v>
       </c>
@@ -35261,10 +36112,13 @@
         <v>28</v>
       </c>
       <c r="L269" t="s">
+        <v>547</v>
+      </c>
+      <c r="M269" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A270" t="s">
         <v>10</v>
       </c>
@@ -35299,10 +36153,13 @@
         <v>29</v>
       </c>
       <c r="L270" t="s">
+        <v>547</v>
+      </c>
+      <c r="M270" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A271" t="s">
         <v>10</v>
       </c>
@@ -35337,10 +36194,13 @@
         <v>30.5</v>
       </c>
       <c r="L271" t="s">
+        <v>547</v>
+      </c>
+      <c r="M271" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A272" t="s">
         <v>10</v>
       </c>
@@ -35375,10 +36235,13 @@
         <v>32</v>
       </c>
       <c r="L272" t="s">
+        <v>547</v>
+      </c>
+      <c r="M272" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A273" t="s">
         <v>10</v>
       </c>
@@ -35413,10 +36276,13 @@
         <v>25</v>
       </c>
       <c r="L273" t="s">
+        <v>547</v>
+      </c>
+      <c r="M273" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A274" t="s">
         <v>10</v>
       </c>
@@ -35451,10 +36317,13 @@
         <v>26</v>
       </c>
       <c r="L274" t="s">
+        <v>547</v>
+      </c>
+      <c r="M274" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
         <v>10</v>
       </c>
@@ -35489,10 +36358,13 @@
         <v>27</v>
       </c>
       <c r="L275" t="s">
+        <v>547</v>
+      </c>
+      <c r="M275" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A276" t="s">
         <v>10</v>
       </c>
@@ -35527,10 +36399,13 @@
         <v>28</v>
       </c>
       <c r="L276" t="s">
+        <v>547</v>
+      </c>
+      <c r="M276" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A277" t="s">
         <v>10</v>
       </c>
@@ -35565,10 +36440,13 @@
         <v>29</v>
       </c>
       <c r="L277" t="s">
+        <v>547</v>
+      </c>
+      <c r="M277" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A278" t="s">
         <v>10</v>
       </c>
@@ -35603,10 +36481,13 @@
         <v>30.5</v>
       </c>
       <c r="L278" t="s">
+        <v>547</v>
+      </c>
+      <c r="M278" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A279" t="s">
         <v>10</v>
       </c>
@@ -35641,10 +36522,13 @@
         <v>32</v>
       </c>
       <c r="L279" t="s">
+        <v>547</v>
+      </c>
+      <c r="M279" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A280" t="s">
         <v>10</v>
       </c>
@@ -35679,10 +36563,13 @@
         <v>26</v>
       </c>
       <c r="L280" t="s">
+        <v>547</v>
+      </c>
+      <c r="M280" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A281" t="s">
         <v>10</v>
       </c>
@@ -35717,10 +36604,13 @@
         <v>27</v>
       </c>
       <c r="L281" t="s">
+        <v>547</v>
+      </c>
+      <c r="M281" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A282" t="s">
         <v>10</v>
       </c>
@@ -35755,10 +36645,13 @@
         <v>28</v>
       </c>
       <c r="L282" t="s">
+        <v>547</v>
+      </c>
+      <c r="M282" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A283" t="s">
         <v>10</v>
       </c>
@@ -35793,10 +36686,13 @@
         <v>29</v>
       </c>
       <c r="L283" t="s">
+        <v>547</v>
+      </c>
+      <c r="M283" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A284" t="s">
         <v>10</v>
       </c>
@@ -35831,10 +36727,13 @@
         <v>30</v>
       </c>
       <c r="L284" t="s">
+        <v>547</v>
+      </c>
+      <c r="M284" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A285" t="s">
         <v>10</v>
       </c>
@@ -35869,10 +36768,13 @@
         <v>31.5</v>
       </c>
       <c r="L285" t="s">
+        <v>547</v>
+      </c>
+      <c r="M285" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A286" t="s">
         <v>10</v>
       </c>
@@ -35907,10 +36809,13 @@
         <v>33</v>
       </c>
       <c r="L286" t="s">
+        <v>547</v>
+      </c>
+      <c r="M286" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A287" t="s">
         <v>56</v>
       </c>
@@ -35945,10 +36850,13 @@
         <v>26</v>
       </c>
       <c r="L287" t="s">
+        <v>544</v>
+      </c>
+      <c r="M287" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A288" t="s">
         <v>56</v>
       </c>
@@ -35983,10 +36891,13 @@
         <v>26.5</v>
       </c>
       <c r="L288" t="s">
+        <v>544</v>
+      </c>
+      <c r="M288" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A289" t="s">
         <v>56</v>
       </c>
@@ -36021,10 +36932,13 @@
         <v>26.7</v>
       </c>
       <c r="L289" t="s">
+        <v>544</v>
+      </c>
+      <c r="M289" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A290" t="s">
         <v>56</v>
       </c>
@@ -36059,10 +36973,13 @@
         <v>27</v>
       </c>
       <c r="L290" t="s">
+        <v>544</v>
+      </c>
+      <c r="M290" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A291" t="s">
         <v>56</v>
       </c>
@@ -36097,10 +37014,13 @@
         <v>27.3</v>
       </c>
       <c r="L291" t="s">
+        <v>544</v>
+      </c>
+      <c r="M291" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A292" t="s">
         <v>56</v>
       </c>
@@ -36135,10 +37055,13 @@
         <v>27.6</v>
       </c>
       <c r="L292" t="s">
+        <v>544</v>
+      </c>
+      <c r="M292" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A293" t="s">
         <v>56</v>
       </c>
@@ -36173,10 +37096,13 @@
         <v>28.2</v>
       </c>
       <c r="L293" t="s">
+        <v>544</v>
+      </c>
+      <c r="M293" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A294" t="s">
         <v>56</v>
       </c>
@@ -36211,10 +37137,13 @@
         <v>22.25</v>
       </c>
       <c r="L294" t="s">
+        <v>544</v>
+      </c>
+      <c r="M294" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A295" t="s">
         <v>56</v>
       </c>
@@ -36249,10 +37178,13 @@
         <v>22.5</v>
       </c>
       <c r="L295" t="s">
+        <v>544</v>
+      </c>
+      <c r="M295" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A296" t="s">
         <v>56</v>
       </c>
@@ -36287,10 +37219,13 @@
         <v>22.75</v>
       </c>
       <c r="L296" t="s">
+        <v>544</v>
+      </c>
+      <c r="M296" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
         <v>56</v>
       </c>
@@ -36325,10 +37260,13 @@
         <v>23</v>
       </c>
       <c r="L297" t="s">
+        <v>544</v>
+      </c>
+      <c r="M297" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A298" t="s">
         <v>56</v>
       </c>
@@ -36363,10 +37301,13 @@
         <v>22.8</v>
       </c>
       <c r="L298" t="s">
+        <v>544</v>
+      </c>
+      <c r="M298" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A299" t="s">
         <v>56</v>
       </c>
@@ -36401,10 +37342,13 @@
         <v>23.6</v>
       </c>
       <c r="L299" t="s">
+        <v>544</v>
+      </c>
+      <c r="M299" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A300" t="s">
         <v>56</v>
       </c>
@@ -36439,10 +37383,13 @@
         <v>23.9</v>
       </c>
       <c r="L300" t="s">
+        <v>544</v>
+      </c>
+      <c r="M300" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A301" t="s">
         <v>56</v>
       </c>
@@ -36477,10 +37424,13 @@
         <v>18</v>
       </c>
       <c r="L301" t="s">
+        <v>548</v>
+      </c>
+      <c r="M301" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A302" t="s">
         <v>56</v>
       </c>
@@ -36515,10 +37465,13 @@
         <v>18.5</v>
       </c>
       <c r="L302" t="s">
+        <v>548</v>
+      </c>
+      <c r="M302" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A303" t="s">
         <v>56</v>
       </c>
@@ -36553,10 +37506,13 @@
         <v>19</v>
       </c>
       <c r="L303" t="s">
+        <v>548</v>
+      </c>
+      <c r="M303" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A304" t="s">
         <v>56</v>
       </c>
@@ -36591,10 +37547,13 @@
         <v>19.5</v>
       </c>
       <c r="L304" t="s">
+        <v>548</v>
+      </c>
+      <c r="M304" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A305" t="s">
         <v>56</v>
       </c>
@@ -36629,10 +37588,13 @@
         <v>20</v>
       </c>
       <c r="L305" t="s">
+        <v>548</v>
+      </c>
+      <c r="M305" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A306" t="s">
         <v>56</v>
       </c>
@@ -36667,10 +37629,13 @@
         <v>23</v>
       </c>
       <c r="L306" t="s">
+        <v>548</v>
+      </c>
+      <c r="M306" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A307" t="s">
         <v>56</v>
       </c>
@@ -36705,10 +37670,13 @@
         <v>23.5</v>
       </c>
       <c r="L307" t="s">
+        <v>548</v>
+      </c>
+      <c r="M307" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A308" t="s">
         <v>56</v>
       </c>
@@ -36743,10 +37711,13 @@
         <v>24</v>
       </c>
       <c r="L308" t="s">
+        <v>548</v>
+      </c>
+      <c r="M308" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A309" t="s">
         <v>56</v>
       </c>
@@ -36781,10 +37752,13 @@
         <v>24.5</v>
       </c>
       <c r="L309" t="s">
+        <v>548</v>
+      </c>
+      <c r="M309" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A310" t="s">
         <v>56</v>
       </c>
@@ -36819,10 +37793,13 @@
         <v>25</v>
       </c>
       <c r="L310" t="s">
+        <v>548</v>
+      </c>
+      <c r="M310" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A311" t="s">
         <v>56</v>
       </c>
@@ -36857,10 +37834,13 @@
         <v>23.8</v>
       </c>
       <c r="L311" t="s">
+        <v>544</v>
+      </c>
+      <c r="M311" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A312" t="s">
         <v>56</v>
       </c>
@@ -36895,10 +37875,13 @@
         <v>24.4</v>
       </c>
       <c r="L312" t="s">
+        <v>544</v>
+      </c>
+      <c r="M312" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A313" t="s">
         <v>56</v>
       </c>
@@ -36933,10 +37916,13 @@
         <v>25</v>
       </c>
       <c r="L313" t="s">
+        <v>544</v>
+      </c>
+      <c r="M313" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A314" t="s">
         <v>56</v>
       </c>
@@ -36971,10 +37957,13 @@
         <v>25.6</v>
       </c>
       <c r="L314" t="s">
+        <v>544</v>
+      </c>
+      <c r="M314" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A315" t="s">
         <v>56</v>
       </c>
@@ -37009,10 +37998,13 @@
         <v>26.2</v>
       </c>
       <c r="L315" t="s">
+        <v>544</v>
+      </c>
+      <c r="M315" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A316" t="s">
         <v>56</v>
       </c>
@@ -37047,10 +38039,13 @@
         <v>17.5</v>
       </c>
       <c r="L316" t="s">
+        <v>544</v>
+      </c>
+      <c r="M316" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A317" t="s">
         <v>56</v>
       </c>
@@ -37085,10 +38080,13 @@
         <v>18</v>
       </c>
       <c r="L317" t="s">
+        <v>544</v>
+      </c>
+      <c r="M317" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A318" t="s">
         <v>56</v>
       </c>
@@ -37123,10 +38121,13 @@
         <v>18.25</v>
       </c>
       <c r="L318" t="s">
+        <v>544</v>
+      </c>
+      <c r="M318" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A319" t="s">
         <v>56</v>
       </c>
@@ -37161,10 +38162,13 @@
         <v>18.5</v>
       </c>
       <c r="L319" t="s">
+        <v>544</v>
+      </c>
+      <c r="M319" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A320" t="s">
         <v>56</v>
       </c>
@@ -37199,10 +38203,13 @@
         <v>18.8</v>
       </c>
       <c r="L320" t="s">
+        <v>544</v>
+      </c>
+      <c r="M320" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A321" t="s">
         <v>56</v>
       </c>
@@ -37237,10 +38244,13 @@
         <v>19.100000000000001</v>
       </c>
       <c r="L321" t="s">
+        <v>544</v>
+      </c>
+      <c r="M321" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A322" t="s">
         <v>56</v>
       </c>
@@ -37275,10 +38285,13 @@
         <v>19.7</v>
       </c>
       <c r="L322" t="s">
+        <v>544</v>
+      </c>
+      <c r="M322" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A323" t="s">
         <v>56</v>
       </c>
@@ -37313,10 +38326,13 @@
         <v>22.4</v>
       </c>
       <c r="L323" t="s">
+        <v>544</v>
+      </c>
+      <c r="M323" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A324" t="s">
         <v>56</v>
       </c>
@@ -37351,10 +38367,13 @@
         <v>23</v>
       </c>
       <c r="L324" t="s">
+        <v>544</v>
+      </c>
+      <c r="M324" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A325" t="s">
         <v>56</v>
       </c>
@@ -37389,10 +38408,13 @@
         <v>23.6</v>
       </c>
       <c r="L325" t="s">
+        <v>544</v>
+      </c>
+      <c r="M325" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A326" t="s">
         <v>56</v>
       </c>
@@ -37427,10 +38449,13 @@
         <v>24.2</v>
       </c>
       <c r="L326" t="s">
+        <v>544</v>
+      </c>
+      <c r="M326" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A327" t="s">
         <v>56</v>
       </c>
@@ -37465,10 +38490,13 @@
         <v>24.8</v>
       </c>
       <c r="L327" t="s">
+        <v>544</v>
+      </c>
+      <c r="M327" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A328" t="s">
         <v>56</v>
       </c>
@@ -37503,10 +38531,13 @@
         <v>27.5</v>
       </c>
       <c r="L328" t="s">
+        <v>549</v>
+      </c>
+      <c r="M328" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A329" t="s">
         <v>56</v>
       </c>
@@ -37541,10 +38572,13 @@
         <v>28.5</v>
       </c>
       <c r="L329" t="s">
+        <v>549</v>
+      </c>
+      <c r="M329" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A330" t="s">
         <v>56</v>
       </c>
@@ -37579,10 +38613,13 @@
         <v>29.5</v>
       </c>
       <c r="L330" t="s">
+        <v>549</v>
+      </c>
+      <c r="M330" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A331" t="s">
         <v>56</v>
       </c>
@@ -37617,10 +38654,13 @@
         <v>26.3</v>
       </c>
       <c r="L331" t="s">
+        <v>544</v>
+      </c>
+      <c r="M331" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A332" t="s">
         <v>56</v>
       </c>
@@ -37655,10 +38695,13 @@
         <v>26.9</v>
       </c>
       <c r="L332" t="s">
+        <v>544</v>
+      </c>
+      <c r="M332" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A333" t="s">
         <v>56</v>
       </c>
@@ -37693,10 +38736,13 @@
         <v>27.5</v>
       </c>
       <c r="L333" t="s">
+        <v>544</v>
+      </c>
+      <c r="M333" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A334" t="s">
         <v>56</v>
       </c>
@@ -37731,10 +38777,13 @@
         <v>28.1</v>
       </c>
       <c r="L334" t="s">
+        <v>544</v>
+      </c>
+      <c r="M334" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A335" t="s">
         <v>56</v>
       </c>
@@ -37769,10 +38818,13 @@
         <v>28.7</v>
       </c>
       <c r="L335" t="s">
+        <v>544</v>
+      </c>
+      <c r="M335" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A336" t="s">
         <v>56</v>
       </c>
@@ -37807,10 +38859,13 @@
         <v>29.3</v>
       </c>
       <c r="L336" t="s">
+        <v>544</v>
+      </c>
+      <c r="M336" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A337" t="s">
         <v>56</v>
       </c>
@@ -37845,10 +38900,13 @@
         <v>29.9</v>
       </c>
       <c r="L337" t="s">
+        <v>544</v>
+      </c>
+      <c r="M337" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A338" t="s">
         <v>56</v>
       </c>
@@ -37883,10 +38941,13 @@
         <v>29</v>
       </c>
       <c r="L338" t="s">
+        <v>549</v>
+      </c>
+      <c r="M338" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A339" t="s">
         <v>56</v>
       </c>
@@ -37921,10 +38982,13 @@
         <v>30</v>
       </c>
       <c r="L339" t="s">
+        <v>549</v>
+      </c>
+      <c r="M339" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A340" t="s">
         <v>56</v>
       </c>
@@ -37959,10 +39023,13 @@
         <v>31</v>
       </c>
       <c r="L340" t="s">
+        <v>549</v>
+      </c>
+      <c r="M340" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A341" t="s">
         <v>56</v>
       </c>
@@ -37997,10 +39064,13 @@
         <v>22.3</v>
       </c>
       <c r="L341" t="s">
+        <v>544</v>
+      </c>
+      <c r="M341" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A342" t="s">
         <v>56</v>
       </c>
@@ -38035,10 +39105,13 @@
         <v>22.9</v>
       </c>
       <c r="L342" t="s">
+        <v>544</v>
+      </c>
+      <c r="M342" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A343" t="s">
         <v>56</v>
       </c>
@@ -38073,10 +39146,13 @@
         <v>23.5</v>
       </c>
       <c r="L343" t="s">
+        <v>544</v>
+      </c>
+      <c r="M343" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A344" t="s">
         <v>56</v>
       </c>
@@ -38111,10 +39187,13 @@
         <v>24.1</v>
       </c>
       <c r="L344" t="s">
+        <v>544</v>
+      </c>
+      <c r="M344" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A345" t="s">
         <v>56</v>
       </c>
@@ -38149,10 +39228,13 @@
         <v>24.7</v>
       </c>
       <c r="L345" t="s">
+        <v>544</v>
+      </c>
+      <c r="M345" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A346" t="s">
         <v>56</v>
       </c>
@@ -38187,10 +39269,13 @@
         <v>25.3</v>
       </c>
       <c r="L346" t="s">
+        <v>544</v>
+      </c>
+      <c r="M346" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A347" t="s">
         <v>56</v>
       </c>
@@ -38225,10 +39310,13 @@
         <v>25.9</v>
       </c>
       <c r="L347" t="s">
+        <v>544</v>
+      </c>
+      <c r="M347" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A348" t="s">
         <v>56</v>
       </c>
@@ -38263,10 +39351,13 @@
         <v>23.4</v>
       </c>
       <c r="L348" t="s">
+        <v>544</v>
+      </c>
+      <c r="M348" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A349" t="s">
         <v>56</v>
       </c>
@@ -38301,10 +39392,13 @@
         <v>24</v>
       </c>
       <c r="L349" t="s">
+        <v>544</v>
+      </c>
+      <c r="M349" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A350" t="s">
         <v>56</v>
       </c>
@@ -38339,10 +39433,13 @@
         <v>24.6</v>
       </c>
       <c r="L350" t="s">
+        <v>544</v>
+      </c>
+      <c r="M350" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A351" t="s">
         <v>56</v>
       </c>
@@ -38377,10 +39474,13 @@
         <v>25.2</v>
       </c>
       <c r="L351" t="s">
+        <v>544</v>
+      </c>
+      <c r="M351" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A352" t="s">
         <v>56</v>
       </c>
@@ -38415,10 +39515,13 @@
         <v>25.8</v>
       </c>
       <c r="L352" t="s">
+        <v>544</v>
+      </c>
+      <c r="M352" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A353" t="s">
         <v>56</v>
       </c>
@@ -38453,10 +39556,13 @@
         <v>26.4</v>
       </c>
       <c r="L353" t="s">
+        <v>544</v>
+      </c>
+      <c r="M353" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A354" t="s">
         <v>56</v>
       </c>
@@ -38491,10 +39597,13 @@
         <v>22.4</v>
       </c>
       <c r="L354" t="s">
+        <v>544</v>
+      </c>
+      <c r="M354" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A355" t="s">
         <v>56</v>
       </c>
@@ -38529,10 +39638,13 @@
         <v>23</v>
       </c>
       <c r="L355" t="s">
+        <v>544</v>
+      </c>
+      <c r="M355" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A356" t="s">
         <v>56</v>
       </c>
@@ -38567,10 +39679,13 @@
         <v>23.6</v>
       </c>
       <c r="L356" t="s">
+        <v>544</v>
+      </c>
+      <c r="M356" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A357" t="s">
         <v>56</v>
       </c>
@@ -38605,10 +39720,13 @@
         <v>24.2</v>
       </c>
       <c r="L357" t="s">
+        <v>544</v>
+      </c>
+      <c r="M357" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A358" t="s">
         <v>56</v>
       </c>
@@ -38643,10 +39761,13 @@
         <v>24.8</v>
       </c>
       <c r="L358" t="s">
+        <v>544</v>
+      </c>
+      <c r="M358" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A359" t="s">
         <v>56</v>
       </c>
@@ -38681,10 +39802,13 @@
         <v>20.8</v>
       </c>
       <c r="L359" t="s">
+        <v>544</v>
+      </c>
+      <c r="M359" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A360" t="s">
         <v>56</v>
       </c>
@@ -38719,10 +39843,13 @@
         <v>21.4</v>
       </c>
       <c r="L360" t="s">
+        <v>544</v>
+      </c>
+      <c r="M360" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A361" t="s">
         <v>56</v>
       </c>
@@ -38757,10 +39884,13 @@
         <v>22</v>
       </c>
       <c r="L361" t="s">
+        <v>544</v>
+      </c>
+      <c r="M361" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A362" t="s">
         <v>56</v>
       </c>
@@ -38795,10 +39925,13 @@
         <v>22.6</v>
       </c>
       <c r="L362" t="s">
+        <v>544</v>
+      </c>
+      <c r="M362" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A363" t="s">
         <v>56</v>
       </c>
@@ -38833,10 +39966,13 @@
         <v>23.2</v>
       </c>
       <c r="L363" t="s">
+        <v>544</v>
+      </c>
+      <c r="M363" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A364" t="s">
         <v>56</v>
       </c>
@@ -38871,10 +40007,13 @@
         <v>23.8</v>
       </c>
       <c r="L364" t="s">
+        <v>544</v>
+      </c>
+      <c r="M364" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A365" t="s">
         <v>56</v>
       </c>
@@ -38909,10 +40048,13 @@
         <v>24.4</v>
       </c>
       <c r="L365" t="s">
+        <v>544</v>
+      </c>
+      <c r="M365" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A366" t="s">
         <v>56</v>
       </c>
@@ -38947,10 +40089,13 @@
         <v>24.8</v>
       </c>
       <c r="L366" t="s">
+        <v>544</v>
+      </c>
+      <c r="M366" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A367" t="s">
         <v>56</v>
       </c>
@@ -38985,10 +40130,13 @@
         <v>25.4</v>
       </c>
       <c r="L367" t="s">
+        <v>544</v>
+      </c>
+      <c r="M367" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A368" t="s">
         <v>56</v>
       </c>
@@ -39023,10 +40171,13 @@
         <v>26</v>
       </c>
       <c r="L368" t="s">
+        <v>544</v>
+      </c>
+      <c r="M368" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A369" t="s">
         <v>56</v>
       </c>
@@ -39061,10 +40212,13 @@
         <v>26.6</v>
       </c>
       <c r="L369" t="s">
+        <v>544</v>
+      </c>
+      <c r="M369" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A370" t="s">
         <v>56</v>
       </c>
@@ -39099,10 +40253,13 @@
         <v>27.2</v>
       </c>
       <c r="L370" t="s">
+        <v>544</v>
+      </c>
+      <c r="M370" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A371" t="s">
         <v>56</v>
       </c>
@@ -39137,10 +40294,13 @@
         <v>27.8</v>
       </c>
       <c r="L371" t="s">
+        <v>544</v>
+      </c>
+      <c r="M371" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A372" t="s">
         <v>56</v>
       </c>
@@ -39175,10 +40335,13 @@
         <v>28.4</v>
       </c>
       <c r="L372" t="s">
+        <v>544</v>
+      </c>
+      <c r="M372" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A373" t="s">
         <v>71</v>
       </c>
@@ -39189,7 +40352,7 @@
         <v>24</v>
       </c>
       <c r="D373" t="s">
-        <v>396</v>
+        <v>550</v>
       </c>
       <c r="E373" t="s">
         <v>16</v>
@@ -39213,10 +40376,13 @@
         <v>25</v>
       </c>
       <c r="L373" t="s">
+        <v>549</v>
+      </c>
+      <c r="M373" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A374" t="s">
         <v>71</v>
       </c>
@@ -39251,10 +40417,13 @@
         <v>25.5</v>
       </c>
       <c r="L374" t="s">
+        <v>549</v>
+      </c>
+      <c r="M374" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A375" t="s">
         <v>71</v>
       </c>
@@ -39289,10 +40458,13 @@
         <v>26</v>
       </c>
       <c r="L375" t="s">
+        <v>549</v>
+      </c>
+      <c r="M375" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A376" t="s">
         <v>71</v>
       </c>
@@ -39327,10 +40499,13 @@
         <v>26.8</v>
       </c>
       <c r="L376" t="s">
+        <v>549</v>
+      </c>
+      <c r="M376" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A377" t="s">
         <v>71</v>
       </c>
@@ -39365,10 +40540,13 @@
         <v>22.9</v>
       </c>
       <c r="L377" t="s">
+        <v>548</v>
+      </c>
+      <c r="M377" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A378" t="s">
         <v>71</v>
       </c>
@@ -39403,10 +40581,13 @@
         <v>23.1</v>
       </c>
       <c r="L378" t="s">
+        <v>548</v>
+      </c>
+      <c r="M378" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A379" t="s">
         <v>71</v>
       </c>
@@ -39441,10 +40622,13 @@
         <v>23.3</v>
       </c>
       <c r="L379" t="s">
+        <v>548</v>
+      </c>
+      <c r="M379" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A380" t="s">
         <v>71</v>
       </c>
@@ -39479,10 +40663,13 @@
         <v>23.5</v>
       </c>
       <c r="L380" t="s">
+        <v>548</v>
+      </c>
+      <c r="M380" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A381" t="s">
         <v>71</v>
       </c>
@@ -39517,10 +40704,13 @@
         <v>23.9</v>
       </c>
       <c r="L381" t="s">
+        <v>548</v>
+      </c>
+      <c r="M381" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A382" t="s">
         <v>71</v>
       </c>
@@ -39555,10 +40745,13 @@
         <v>24.3</v>
       </c>
       <c r="L382" t="s">
+        <v>548</v>
+      </c>
+      <c r="M382" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A383" t="s">
         <v>71</v>
       </c>
@@ -39593,10 +40786,13 @@
         <v>24</v>
       </c>
       <c r="L383" t="s">
+        <v>549</v>
+      </c>
+      <c r="M383" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A384" t="s">
         <v>71</v>
       </c>
@@ -39631,10 +40827,13 @@
         <v>24.5</v>
       </c>
       <c r="L384" t="s">
+        <v>549</v>
+      </c>
+      <c r="M384" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A385" t="s">
         <v>71</v>
       </c>
@@ -39645,7 +40844,7 @@
         <v>24</v>
       </c>
       <c r="D385" t="s">
-        <v>405</v>
+        <v>551</v>
       </c>
       <c r="E385" t="s">
         <v>18</v>
@@ -39669,10 +40868,13 @@
         <v>25</v>
       </c>
       <c r="L385" t="s">
+        <v>549</v>
+      </c>
+      <c r="M385" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A386" t="s">
         <v>71</v>
       </c>
@@ -39707,10 +40909,13 @@
         <v>25.8</v>
       </c>
       <c r="L386" t="s">
+        <v>549</v>
+      </c>
+      <c r="M386" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A387" t="s">
         <v>71</v>
       </c>
@@ -39721,7 +40926,7 @@
         <v>24</v>
       </c>
       <c r="D387" t="s">
-        <v>407</v>
+        <v>552</v>
       </c>
       <c r="E387" t="s">
         <v>408</v>
@@ -39745,10 +40950,13 @@
         <v>22.2</v>
       </c>
       <c r="L387" t="s">
+        <v>544</v>
+      </c>
+      <c r="M387" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A388" t="s">
         <v>71</v>
       </c>
@@ -39783,10 +40991,13 @@
         <v>22.4</v>
       </c>
       <c r="L388" t="s">
+        <v>544</v>
+      </c>
+      <c r="M388" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A389" t="s">
         <v>71</v>
       </c>
@@ -39821,10 +41032,13 @@
         <v>22.6</v>
       </c>
       <c r="L389" t="s">
+        <v>544</v>
+      </c>
+      <c r="M389" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A390" t="s">
         <v>71</v>
       </c>
@@ -39859,10 +41073,13 @@
         <v>22.8</v>
       </c>
       <c r="L390" t="s">
+        <v>544</v>
+      </c>
+      <c r="M390" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A391" t="s">
         <v>71</v>
       </c>
@@ -39897,10 +41114,13 @@
         <v>23</v>
       </c>
       <c r="L391" t="s">
+        <v>544</v>
+      </c>
+      <c r="M391" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A392" t="s">
         <v>71</v>
       </c>
@@ -39935,10 +41155,13 @@
         <v>23.4</v>
       </c>
       <c r="L392" t="s">
+        <v>544</v>
+      </c>
+      <c r="M392" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A393" t="s">
         <v>71</v>
       </c>
@@ -39973,10 +41196,13 @@
         <v>23.8</v>
       </c>
       <c r="L393" t="s">
+        <v>544</v>
+      </c>
+      <c r="M393" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A394" t="s">
         <v>71</v>
       </c>
@@ -40011,10 +41237,13 @@
         <v>23.5</v>
       </c>
       <c r="L394" t="s">
+        <v>549</v>
+      </c>
+      <c r="M394" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A395" t="s">
         <v>71</v>
       </c>
@@ -40049,10 +41278,13 @@
         <v>24</v>
       </c>
       <c r="L395" t="s">
+        <v>549</v>
+      </c>
+      <c r="M395" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A396" t="s">
         <v>71</v>
       </c>
@@ -40087,10 +41319,13 @@
         <v>24.5</v>
       </c>
       <c r="L396" t="s">
+        <v>549</v>
+      </c>
+      <c r="M396" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A397" t="s">
         <v>71</v>
       </c>
@@ -40125,10 +41360,13 @@
         <v>25.3</v>
       </c>
       <c r="L397" t="s">
+        <v>549</v>
+      </c>
+      <c r="M397" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A398" t="s">
         <v>71</v>
       </c>
@@ -40163,10 +41401,13 @@
         <v>27.2</v>
       </c>
       <c r="L398" t="s">
+        <v>544</v>
+      </c>
+      <c r="M398" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A399" t="s">
         <v>71</v>
       </c>
@@ -40201,10 +41442,13 @@
         <v>27.4</v>
       </c>
       <c r="L399" t="s">
+        <v>544</v>
+      </c>
+      <c r="M399" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A400" t="s">
         <v>71</v>
       </c>
@@ -40239,10 +41483,13 @@
         <v>27.6</v>
       </c>
       <c r="L400" t="s">
+        <v>544</v>
+      </c>
+      <c r="M400" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A401" t="s">
         <v>71</v>
       </c>
@@ -40277,10 +41524,13 @@
         <v>27.8</v>
       </c>
       <c r="L401" t="s">
+        <v>544</v>
+      </c>
+      <c r="M401" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A402" t="s">
         <v>71</v>
       </c>
@@ -40315,10 +41565,13 @@
         <v>28</v>
       </c>
       <c r="L402" t="s">
+        <v>544</v>
+      </c>
+      <c r="M402" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A403" t="s">
         <v>71</v>
       </c>
@@ -40353,10 +41606,13 @@
         <v>28.4</v>
       </c>
       <c r="L403" t="s">
+        <v>544</v>
+      </c>
+      <c r="M403" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A404" t="s">
         <v>71</v>
       </c>
@@ -40391,10 +41647,13 @@
         <v>28.8</v>
       </c>
       <c r="L404" t="s">
+        <v>544</v>
+      </c>
+      <c r="M404" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A405" t="s">
         <v>71</v>
       </c>
@@ -40429,10 +41688,13 @@
         <v>24.4</v>
       </c>
       <c r="L405" t="s">
+        <v>544</v>
+      </c>
+      <c r="M405" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A406" t="s">
         <v>71</v>
       </c>
@@ -40467,10 +41729,13 @@
         <v>24.6</v>
       </c>
       <c r="L406" t="s">
+        <v>544</v>
+      </c>
+      <c r="M406" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A407" t="s">
         <v>71</v>
       </c>
@@ -40505,10 +41770,13 @@
         <v>24.8</v>
       </c>
       <c r="L407" t="s">
+        <v>544</v>
+      </c>
+      <c r="M407" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A408" t="s">
         <v>71</v>
       </c>
@@ -40543,10 +41811,13 @@
         <v>25</v>
       </c>
       <c r="L408" t="s">
+        <v>544</v>
+      </c>
+      <c r="M408" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A409" t="s">
         <v>71</v>
       </c>
@@ -40581,10 +41852,13 @@
         <v>25.4</v>
       </c>
       <c r="L409" t="s">
+        <v>544</v>
+      </c>
+      <c r="M409" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A410" t="s">
         <v>71</v>
       </c>
@@ -40619,10 +41893,13 @@
         <v>18.899999999999999</v>
       </c>
       <c r="L410" t="s">
+        <v>544</v>
+      </c>
+      <c r="M410" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A411" t="s">
         <v>71</v>
       </c>
@@ -40657,10 +41934,13 @@
         <v>19.100000000000001</v>
       </c>
       <c r="L411" t="s">
+        <v>544</v>
+      </c>
+      <c r="M411" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A412" t="s">
         <v>71</v>
       </c>
@@ -40695,10 +41975,13 @@
         <v>19.3</v>
       </c>
       <c r="L412" t="s">
+        <v>544</v>
+      </c>
+      <c r="M412" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A413" t="s">
         <v>71</v>
       </c>
@@ -40733,10 +42016,13 @@
         <v>19.5</v>
       </c>
       <c r="L413" t="s">
+        <v>544</v>
+      </c>
+      <c r="M413" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A414" t="s">
         <v>71</v>
       </c>
@@ -40771,10 +42057,13 @@
         <v>19.899999999999999</v>
       </c>
       <c r="L414" t="s">
+        <v>544</v>
+      </c>
+      <c r="M414" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A415" t="s">
         <v>71</v>
       </c>
@@ -40809,10 +42098,13 @@
         <v>20.2</v>
       </c>
       <c r="L415" t="s">
+        <v>544</v>
+      </c>
+      <c r="M415" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A416" t="s">
         <v>71</v>
       </c>
@@ -40847,10 +42139,13 @@
         <v>18.3</v>
       </c>
       <c r="L416" t="s">
+        <v>548</v>
+      </c>
+      <c r="M416" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A417" t="s">
         <v>71</v>
       </c>
@@ -40885,10 +42180,13 @@
         <v>18.5</v>
       </c>
       <c r="L417" t="s">
+        <v>548</v>
+      </c>
+      <c r="M417" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A418" t="s">
         <v>71</v>
       </c>
@@ -40923,10 +42221,13 @@
         <v>18.8</v>
       </c>
       <c r="L418" t="s">
+        <v>548</v>
+      </c>
+      <c r="M418" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A419" t="s">
         <v>71</v>
       </c>
@@ -40961,10 +42262,13 @@
         <v>19</v>
       </c>
       <c r="L419" t="s">
+        <v>548</v>
+      </c>
+      <c r="M419" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A420" t="s">
         <v>71</v>
       </c>
@@ -40999,10 +42303,13 @@
         <v>19.399999999999999</v>
       </c>
       <c r="L420" t="s">
+        <v>548</v>
+      </c>
+      <c r="M420" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A421" t="s">
         <v>71</v>
       </c>
@@ -41037,10 +42344,13 @@
         <v>19.7</v>
       </c>
       <c r="L421" t="s">
+        <v>548</v>
+      </c>
+      <c r="M421" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A422" t="s">
         <v>71</v>
       </c>
@@ -41075,10 +42385,13 @@
         <v>27.5</v>
       </c>
       <c r="L422" t="s">
+        <v>553</v>
+      </c>
+      <c r="M422" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A423" t="s">
         <v>71</v>
       </c>
@@ -41113,10 +42426,13 @@
         <v>28.5</v>
       </c>
       <c r="L423" t="s">
+        <v>553</v>
+      </c>
+      <c r="M423" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A424" t="s">
         <v>71</v>
       </c>
@@ -41151,10 +42467,13 @@
         <v>29.5</v>
       </c>
       <c r="L424" t="s">
+        <v>553</v>
+      </c>
+      <c r="M424" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A425" t="s">
         <v>71</v>
       </c>
@@ -41189,10 +42508,13 @@
         <v>30.5</v>
       </c>
       <c r="L425" t="s">
+        <v>553</v>
+      </c>
+      <c r="M425" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A426" t="s">
         <v>71</v>
       </c>
@@ -41227,10 +42549,13 @@
         <v>31.8</v>
       </c>
       <c r="L426" t="s">
+        <v>553</v>
+      </c>
+      <c r="M426" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A427" t="s">
         <v>71</v>
       </c>
@@ -41265,10 +42590,13 @@
         <v>28.2</v>
       </c>
       <c r="L427" t="s">
+        <v>549</v>
+      </c>
+      <c r="M427" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A428" t="s">
         <v>71</v>
       </c>
@@ -41303,10 +42631,13 @@
         <v>29.2</v>
       </c>
       <c r="L428" t="s">
+        <v>549</v>
+      </c>
+      <c r="M428" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A429" t="s">
         <v>71</v>
       </c>
@@ -41341,10 +42672,13 @@
         <v>30.2</v>
       </c>
       <c r="L429" t="s">
+        <v>549</v>
+      </c>
+      <c r="M429" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A430" t="s">
         <v>71</v>
       </c>
@@ -41379,10 +42713,13 @@
         <v>31.2</v>
       </c>
       <c r="L430" t="s">
+        <v>549</v>
+      </c>
+      <c r="M430" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A431" t="s">
         <v>71</v>
       </c>
@@ -41417,10 +42754,13 @@
         <v>32.5</v>
       </c>
       <c r="L431" t="s">
+        <v>549</v>
+      </c>
+      <c r="M431" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A432" t="s">
         <v>71</v>
       </c>
@@ -41455,10 +42795,13 @@
         <v>26</v>
       </c>
       <c r="L432" t="s">
+        <v>544</v>
+      </c>
+      <c r="M432" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A433" t="s">
         <v>71</v>
       </c>
@@ -41493,10 +42836,13 @@
         <v>27</v>
       </c>
       <c r="L433" t="s">
+        <v>544</v>
+      </c>
+      <c r="M433" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A434" t="s">
         <v>71</v>
       </c>
@@ -41531,10 +42877,13 @@
         <v>28</v>
       </c>
       <c r="L434" t="s">
+        <v>544</v>
+      </c>
+      <c r="M434" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A435" t="s">
         <v>71</v>
       </c>
@@ -41569,10 +42918,13 @@
         <v>29</v>
       </c>
       <c r="L435" t="s">
+        <v>544</v>
+      </c>
+      <c r="M435" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A436" t="s">
         <v>71</v>
       </c>
@@ -41607,10 +42959,13 @@
         <v>30.3</v>
       </c>
       <c r="L436" t="s">
+        <v>544</v>
+      </c>
+      <c r="M436" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A437" t="s">
         <v>71</v>
       </c>
@@ -41645,10 +43000,13 @@
         <v>27.5</v>
       </c>
       <c r="L437" t="s">
+        <v>549</v>
+      </c>
+      <c r="M437" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A438" t="s">
         <v>71</v>
       </c>
@@ -41683,10 +43041,13 @@
         <v>28.5</v>
       </c>
       <c r="L438" t="s">
+        <v>549</v>
+      </c>
+      <c r="M438" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A439" t="s">
         <v>71</v>
       </c>
@@ -41721,10 +43082,13 @@
         <v>29.5</v>
       </c>
       <c r="L439" t="s">
+        <v>549</v>
+      </c>
+      <c r="M439" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A440" t="s">
         <v>71</v>
       </c>
@@ -41759,10 +43123,13 @@
         <v>30.5</v>
       </c>
       <c r="L440" t="s">
+        <v>549</v>
+      </c>
+      <c r="M440" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A441" t="s">
         <v>71</v>
       </c>
@@ -41797,10 +43164,13 @@
         <v>31.8</v>
       </c>
       <c r="L441" t="s">
+        <v>549</v>
+      </c>
+      <c r="M441" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A442" t="s">
         <v>71</v>
       </c>
@@ -41835,10 +43205,13 @@
         <v>25.5</v>
       </c>
       <c r="L442" t="s">
+        <v>544</v>
+      </c>
+      <c r="M442" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A443" t="s">
         <v>71</v>
       </c>
@@ -41873,10 +43246,13 @@
         <v>26.5</v>
       </c>
       <c r="L443" t="s">
+        <v>544</v>
+      </c>
+      <c r="M443" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A444" t="s">
         <v>71</v>
       </c>
@@ -41911,10 +43287,13 @@
         <v>27.5</v>
       </c>
       <c r="L444" t="s">
+        <v>544</v>
+      </c>
+      <c r="M444" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A445" t="s">
         <v>71</v>
       </c>
@@ -41949,10 +43328,13 @@
         <v>28.5</v>
       </c>
       <c r="L445" t="s">
+        <v>544</v>
+      </c>
+      <c r="M445" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A446" t="s">
         <v>71</v>
       </c>
@@ -41987,10 +43369,13 @@
         <v>29.8</v>
       </c>
       <c r="L446" t="s">
+        <v>544</v>
+      </c>
+      <c r="M446" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A447" t="s">
         <v>71</v>
       </c>
@@ -42025,10 +43410,13 @@
         <v>26</v>
       </c>
       <c r="L447" t="s">
+        <v>544</v>
+      </c>
+      <c r="M447" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A448" t="s">
         <v>71</v>
       </c>
@@ -42063,10 +43451,13 @@
         <v>27</v>
       </c>
       <c r="L448" t="s">
+        <v>544</v>
+      </c>
+      <c r="M448" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A449" t="s">
         <v>71</v>
       </c>
@@ -42101,10 +43492,13 @@
         <v>28</v>
       </c>
       <c r="L449" t="s">
+        <v>544</v>
+      </c>
+      <c r="M449" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A450" t="s">
         <v>71</v>
       </c>
@@ -42139,10 +43533,13 @@
         <v>29</v>
       </c>
       <c r="L450" t="s">
+        <v>544</v>
+      </c>
+      <c r="M450" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A451" t="s">
         <v>71</v>
       </c>
@@ -42177,10 +43574,13 @@
         <v>30.3</v>
       </c>
       <c r="L451" t="s">
+        <v>544</v>
+      </c>
+      <c r="M451" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A452" t="s">
         <v>71</v>
       </c>
@@ -42215,10 +43615,13 @@
         <v>24.2</v>
       </c>
       <c r="L452" t="s">
+        <v>544</v>
+      </c>
+      <c r="M452" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A453" t="s">
         <v>71</v>
       </c>
@@ -42253,10 +43656,13 @@
         <v>25.2</v>
       </c>
       <c r="L453" t="s">
+        <v>544</v>
+      </c>
+      <c r="M453" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A454" t="s">
         <v>71</v>
       </c>
@@ -42291,10 +43697,13 @@
         <v>26.2</v>
       </c>
       <c r="L454" t="s">
+        <v>544</v>
+      </c>
+      <c r="M454" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A455" t="s">
         <v>71</v>
       </c>
@@ -42329,10 +43738,13 @@
         <v>25.5</v>
       </c>
       <c r="L455" t="s">
+        <v>544</v>
+      </c>
+      <c r="M455" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A456" t="s">
         <v>71</v>
       </c>
@@ -42367,10 +43779,13 @@
         <v>26</v>
       </c>
       <c r="L456" t="s">
+        <v>544</v>
+      </c>
+      <c r="M456" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A457" t="s">
         <v>71</v>
       </c>
@@ -42405,10 +43820,13 @@
         <v>26.5</v>
       </c>
       <c r="L457" t="s">
+        <v>544</v>
+      </c>
+      <c r="M457" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A458" t="s">
         <v>71</v>
       </c>
@@ -42443,10 +43861,13 @@
         <v>27</v>
       </c>
       <c r="L458" t="s">
+        <v>544</v>
+      </c>
+      <c r="M458" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A459" t="s">
         <v>71</v>
       </c>
@@ -42481,10 +43902,13 @@
         <v>27.6</v>
       </c>
       <c r="L459" t="s">
+        <v>544</v>
+      </c>
+      <c r="M459" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A460" t="s">
         <v>89</v>
       </c>
@@ -42519,10 +43943,13 @@
         <v>19.100000000000001</v>
       </c>
       <c r="L460" t="s">
+        <v>544</v>
+      </c>
+      <c r="M460" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A461" t="s">
         <v>89</v>
       </c>
@@ -42557,10 +43984,13 @@
         <v>19.399999999999999</v>
       </c>
       <c r="L461" t="s">
+        <v>544</v>
+      </c>
+      <c r="M461" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A462" t="s">
         <v>89</v>
       </c>
@@ -42595,10 +44025,13 @@
         <v>19.7</v>
       </c>
       <c r="L462" t="s">
+        <v>544</v>
+      </c>
+      <c r="M462" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A463" t="s">
         <v>89</v>
       </c>
@@ -42633,10 +44066,13 @@
         <v>20</v>
       </c>
       <c r="L463" t="s">
+        <v>544</v>
+      </c>
+      <c r="M463" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A464" t="s">
         <v>89</v>
       </c>
@@ -42671,10 +44107,13 @@
         <v>20.3</v>
       </c>
       <c r="L464" t="s">
+        <v>544</v>
+      </c>
+      <c r="M464" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A465" t="s">
         <v>89</v>
       </c>
@@ -42709,10 +44148,13 @@
         <v>20.6</v>
       </c>
       <c r="L465" t="s">
+        <v>544</v>
+      </c>
+      <c r="M465" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A466" t="s">
         <v>89</v>
       </c>
@@ -42747,10 +44189,13 @@
         <v>21.2</v>
       </c>
       <c r="L466" t="s">
+        <v>544</v>
+      </c>
+      <c r="M466" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A467" t="s">
         <v>89</v>
       </c>
@@ -42785,10 +44230,13 @@
         <v>21.8</v>
       </c>
       <c r="L467" t="s">
+        <v>544</v>
+      </c>
+      <c r="M467" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A468" t="s">
         <v>89</v>
       </c>
@@ -42823,10 +44271,13 @@
         <v>17.850000000000001</v>
       </c>
       <c r="L468" t="s">
+        <v>544</v>
+      </c>
+      <c r="M468" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A469" t="s">
         <v>89</v>
       </c>
@@ -42861,10 +44312,13 @@
         <v>18.149999999999999</v>
       </c>
       <c r="L469" t="s">
+        <v>544</v>
+      </c>
+      <c r="M469" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A470" t="s">
         <v>89</v>
       </c>
@@ -42899,10 +44353,13 @@
         <v>18.45</v>
       </c>
       <c r="L470" t="s">
+        <v>544</v>
+      </c>
+      <c r="M470" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A471" t="s">
         <v>89</v>
       </c>
@@ -42937,10 +44394,13 @@
         <v>18.75</v>
       </c>
       <c r="L471" t="s">
+        <v>544</v>
+      </c>
+      <c r="M471" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A472" t="s">
         <v>89</v>
       </c>
@@ -42975,10 +44435,13 @@
         <v>19.05</v>
       </c>
       <c r="L472" t="s">
+        <v>544</v>
+      </c>
+      <c r="M472" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A473" t="s">
         <v>89</v>
       </c>
@@ -43013,10 +44476,13 @@
         <v>19.350000000000001</v>
       </c>
       <c r="L473" t="s">
+        <v>544</v>
+      </c>
+      <c r="M473" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A474" t="s">
         <v>89</v>
       </c>
@@ -43051,10 +44517,13 @@
         <v>19.95</v>
       </c>
       <c r="L474" t="s">
+        <v>544</v>
+      </c>
+      <c r="M474" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A475" t="s">
         <v>89</v>
       </c>
@@ -43089,10 +44558,13 @@
         <v>22.8</v>
       </c>
       <c r="L475" t="s">
+        <v>544</v>
+      </c>
+      <c r="M475" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A476" t="s">
         <v>89</v>
       </c>
@@ -43127,10 +44599,13 @@
         <v>23.1</v>
       </c>
       <c r="L476" t="s">
+        <v>544</v>
+      </c>
+      <c r="M476" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A477" t="s">
         <v>89</v>
       </c>
@@ -43165,10 +44640,13 @@
         <v>23.4</v>
       </c>
       <c r="L477" t="s">
+        <v>544</v>
+      </c>
+      <c r="M477" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A478" t="s">
         <v>89</v>
       </c>
@@ -43203,10 +44681,13 @@
         <v>23.7</v>
       </c>
       <c r="L478" t="s">
+        <v>544</v>
+      </c>
+      <c r="M478" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A479" t="s">
         <v>89</v>
       </c>
@@ -43241,10 +44722,13 @@
         <v>24</v>
       </c>
       <c r="L479" t="s">
+        <v>544</v>
+      </c>
+      <c r="M479" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A480" t="s">
         <v>89</v>
       </c>
@@ -43279,10 +44763,13 @@
         <v>24.3</v>
       </c>
       <c r="L480" t="s">
+        <v>544</v>
+      </c>
+      <c r="M480" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A481" t="s">
         <v>89</v>
       </c>
@@ -43317,10 +44804,13 @@
         <v>24.6</v>
       </c>
       <c r="L481" t="s">
+        <v>544</v>
+      </c>
+      <c r="M481" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A482" t="s">
         <v>89</v>
       </c>
@@ -43355,10 +44845,13 @@
         <v>25.2</v>
       </c>
       <c r="L482" t="s">
+        <v>544</v>
+      </c>
+      <c r="M482" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A483" t="s">
         <v>89</v>
       </c>
@@ -43393,10 +44886,13 @@
         <v>25.8</v>
       </c>
       <c r="L483" t="s">
+        <v>544</v>
+      </c>
+      <c r="M483" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A484" t="s">
         <v>89</v>
       </c>
@@ -43431,10 +44927,13 @@
         <v>18.100000000000001</v>
       </c>
       <c r="L484" t="s">
+        <v>549</v>
+      </c>
+      <c r="M484" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A485" t="s">
         <v>89</v>
       </c>
@@ -43469,10 +44968,13 @@
         <v>18.399999999999999</v>
       </c>
       <c r="L485" t="s">
+        <v>549</v>
+      </c>
+      <c r="M485" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A486" t="s">
         <v>89</v>
       </c>
@@ -43507,10 +45009,13 @@
         <v>18.7</v>
       </c>
       <c r="L486" t="s">
+        <v>549</v>
+      </c>
+      <c r="M486" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A487" t="s">
         <v>89</v>
       </c>
@@ -43545,10 +45050,13 @@
         <v>19</v>
       </c>
       <c r="L487" t="s">
+        <v>549</v>
+      </c>
+      <c r="M487" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A488" t="s">
         <v>89</v>
       </c>
@@ -43583,10 +45091,13 @@
         <v>19.3</v>
       </c>
       <c r="L488" t="s">
+        <v>549</v>
+      </c>
+      <c r="M488" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A489" t="s">
         <v>89</v>
       </c>
@@ -43621,10 +45132,13 @@
         <v>19.600000000000001</v>
       </c>
       <c r="L489" t="s">
+        <v>549</v>
+      </c>
+      <c r="M489" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A490" t="s">
         <v>89</v>
       </c>
@@ -43659,10 +45173,13 @@
         <v>20.2</v>
       </c>
       <c r="L490" t="s">
+        <v>549</v>
+      </c>
+      <c r="M490" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A491" t="s">
         <v>89</v>
       </c>
@@ -43697,10 +45214,13 @@
         <v>20.8</v>
       </c>
       <c r="L491" t="s">
+        <v>549</v>
+      </c>
+      <c r="M491" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A492" t="s">
         <v>89</v>
       </c>
@@ -43735,10 +45255,13 @@
         <v>21.4</v>
       </c>
       <c r="L492" t="s">
+        <v>549</v>
+      </c>
+      <c r="M492" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A493" t="s">
         <v>89</v>
       </c>
@@ -43773,10 +45296,13 @@
         <v>24.55</v>
       </c>
       <c r="L493" t="s">
+        <v>549</v>
+      </c>
+      <c r="M493" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A494" t="s">
         <v>89</v>
       </c>
@@ -43811,10 +45337,13 @@
         <v>25.15</v>
       </c>
       <c r="L494" t="s">
+        <v>549</v>
+      </c>
+      <c r="M494" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A495" t="s">
         <v>89</v>
       </c>
@@ -43849,10 +45378,13 @@
         <v>25.75</v>
       </c>
       <c r="L495" t="s">
+        <v>549</v>
+      </c>
+      <c r="M495" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A496" t="s">
         <v>89</v>
       </c>
@@ -43887,10 +45419,13 @@
         <v>26.35</v>
       </c>
       <c r="L496" t="s">
+        <v>549</v>
+      </c>
+      <c r="M496" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="497" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A497" t="s">
         <v>89</v>
       </c>
@@ -43925,10 +45460,13 @@
         <v>27.1</v>
       </c>
       <c r="L497" t="s">
+        <v>549</v>
+      </c>
+      <c r="M497" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A498" t="s">
         <v>89</v>
       </c>
@@ -43963,10 +45501,13 @@
         <v>27.85</v>
       </c>
       <c r="L498" t="s">
+        <v>549</v>
+      </c>
+      <c r="M498" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A499" t="s">
         <v>89</v>
       </c>
@@ -44001,10 +45542,13 @@
         <v>18.399999999999999</v>
       </c>
       <c r="L499" t="s">
+        <v>544</v>
+      </c>
+      <c r="M499" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A500" t="s">
         <v>89</v>
       </c>
@@ -44039,10 +45583,13 @@
         <v>18.7</v>
       </c>
       <c r="L500" t="s">
+        <v>544</v>
+      </c>
+      <c r="M500" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A501" t="s">
         <v>89</v>
       </c>
@@ -44077,10 +45624,13 @@
         <v>19</v>
       </c>
       <c r="L501" t="s">
+        <v>544</v>
+      </c>
+      <c r="M501" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A502" t="s">
         <v>89</v>
       </c>
@@ -44115,10 +45665,13 @@
         <v>19.3</v>
       </c>
       <c r="L502" t="s">
+        <v>544</v>
+      </c>
+      <c r="M502" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A503" t="s">
         <v>89</v>
       </c>
@@ -44153,10 +45706,13 @@
         <v>19.600000000000001</v>
       </c>
       <c r="L503" t="s">
+        <v>544</v>
+      </c>
+      <c r="M503" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A504" t="s">
         <v>89</v>
       </c>
@@ -44191,10 +45747,13 @@
         <v>20.2</v>
       </c>
       <c r="L504" t="s">
+        <v>544</v>
+      </c>
+      <c r="M504" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A505" t="s">
         <v>89</v>
       </c>
@@ -44229,10 +45788,13 @@
         <v>20.8</v>
       </c>
       <c r="L505" t="s">
+        <v>544</v>
+      </c>
+      <c r="M505" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A506" t="s">
         <v>89</v>
       </c>
@@ -44267,10 +45829,13 @@
         <v>21.1</v>
       </c>
       <c r="L506" t="s">
+        <v>544</v>
+      </c>
+      <c r="M506" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A507" t="s">
         <v>89</v>
       </c>
@@ -44305,10 +45870,13 @@
         <v>21.8</v>
       </c>
       <c r="L507" t="s">
+        <v>549</v>
+      </c>
+      <c r="M507" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A508" t="s">
         <v>89</v>
       </c>
@@ -44343,10 +45911,13 @@
         <v>22.4</v>
       </c>
       <c r="L508" t="s">
+        <v>549</v>
+      </c>
+      <c r="M508" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A509" t="s">
         <v>89</v>
       </c>
@@ -44381,10 +45952,13 @@
         <v>23</v>
       </c>
       <c r="L509" t="s">
+        <v>549</v>
+      </c>
+      <c r="M509" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A510" t="s">
         <v>89</v>
       </c>
@@ -44419,10 +45993,13 @@
         <v>23.6</v>
       </c>
       <c r="L510" t="s">
+        <v>549</v>
+      </c>
+      <c r="M510" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A511" t="s">
         <v>89</v>
       </c>
@@ -44457,10 +46034,13 @@
         <v>24.2</v>
       </c>
       <c r="L511" t="s">
+        <v>549</v>
+      </c>
+      <c r="M511" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A512" t="s">
         <v>89</v>
       </c>
@@ -44495,10 +46075,13 @@
         <v>24.8</v>
       </c>
       <c r="L512" t="s">
+        <v>549</v>
+      </c>
+      <c r="M512" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A513" t="s">
         <v>89</v>
       </c>
@@ -44533,10 +46116,13 @@
         <v>19.899999999999999</v>
       </c>
       <c r="L513" t="s">
+        <v>544</v>
+      </c>
+      <c r="M513" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A514" t="s">
         <v>89</v>
       </c>
@@ -44571,10 +46157,13 @@
         <v>20.5</v>
       </c>
       <c r="L514" t="s">
+        <v>544</v>
+      </c>
+      <c r="M514" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A515" t="s">
         <v>89</v>
       </c>
@@ -44609,10 +46198,13 @@
         <v>21.1</v>
       </c>
       <c r="L515" t="s">
+        <v>544</v>
+      </c>
+      <c r="M515" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A516" t="s">
         <v>89</v>
       </c>
@@ -44647,10 +46239,13 @@
         <v>21.7</v>
       </c>
       <c r="L516" t="s">
+        <v>544</v>
+      </c>
+      <c r="M516" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A517" t="s">
         <v>89</v>
       </c>
@@ -44685,10 +46280,13 @@
         <v>22.3</v>
       </c>
       <c r="L517" t="s">
+        <v>544</v>
+      </c>
+      <c r="M517" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A518" t="s">
         <v>89</v>
       </c>
@@ -44723,10 +46321,13 @@
         <v>28</v>
       </c>
       <c r="L518" t="s">
+        <v>549</v>
+      </c>
+      <c r="M518" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A519" t="s">
         <v>89</v>
       </c>
@@ -44761,10 +46362,13 @@
         <v>28.5</v>
       </c>
       <c r="L519" t="s">
+        <v>549</v>
+      </c>
+      <c r="M519" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A520" t="s">
         <v>89</v>
       </c>
@@ -44799,10 +46403,13 @@
         <v>29</v>
       </c>
       <c r="L520" t="s">
+        <v>549</v>
+      </c>
+      <c r="M520" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A521" t="s">
         <v>89</v>
       </c>
@@ -44837,10 +46444,13 @@
         <v>30</v>
       </c>
       <c r="L521" t="s">
+        <v>549</v>
+      </c>
+      <c r="M521" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A522" t="s">
         <v>89</v>
       </c>
@@ -44875,10 +46485,13 @@
         <v>31</v>
       </c>
       <c r="L522" t="s">
+        <v>549</v>
+      </c>
+      <c r="M522" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A523" t="s">
         <v>89</v>
       </c>
@@ -44913,10 +46526,13 @@
         <v>32.299999999999997</v>
       </c>
       <c r="L523" t="s">
+        <v>549</v>
+      </c>
+      <c r="M523" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A524" t="s">
         <v>89</v>
       </c>
@@ -44951,10 +46567,13 @@
         <v>33.6</v>
       </c>
       <c r="L524" t="s">
+        <v>549</v>
+      </c>
+      <c r="M524" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A525" t="s">
         <v>89</v>
       </c>
@@ -44989,10 +46608,13 @@
         <v>28</v>
       </c>
       <c r="L525" t="s">
+        <v>549</v>
+      </c>
+      <c r="M525" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A526" t="s">
         <v>89</v>
       </c>
@@ -45027,10 +46649,13 @@
         <v>28.5</v>
       </c>
       <c r="L526" t="s">
+        <v>549</v>
+      </c>
+      <c r="M526" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A527" t="s">
         <v>89</v>
       </c>
@@ -45065,10 +46690,13 @@
         <v>29</v>
       </c>
       <c r="L527" t="s">
+        <v>549</v>
+      </c>
+      <c r="M527" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A528" t="s">
         <v>89</v>
       </c>
@@ -45103,10 +46731,13 @@
         <v>30</v>
       </c>
       <c r="L528" t="s">
+        <v>549</v>
+      </c>
+      <c r="M528" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A529" t="s">
         <v>89</v>
       </c>
@@ -45141,10 +46772,13 @@
         <v>31</v>
       </c>
       <c r="L529" t="s">
+        <v>549</v>
+      </c>
+      <c r="M529" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A530" t="s">
         <v>89</v>
       </c>
@@ -45179,10 +46813,13 @@
         <v>32.299999999999997</v>
       </c>
       <c r="L530" t="s">
+        <v>549</v>
+      </c>
+      <c r="M530" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A531" t="s">
         <v>89</v>
       </c>
@@ -45217,10 +46854,13 @@
         <v>33.6</v>
       </c>
       <c r="L531" t="s">
+        <v>549</v>
+      </c>
+      <c r="M531" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A532" t="s">
         <v>89</v>
       </c>
@@ -45255,10 +46895,13 @@
         <v>18.2</v>
       </c>
       <c r="L532" t="s">
+        <v>544</v>
+      </c>
+      <c r="M532" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A533" t="s">
         <v>89</v>
       </c>
@@ -45293,10 +46936,13 @@
         <v>18.5</v>
       </c>
       <c r="L533" t="s">
+        <v>544</v>
+      </c>
+      <c r="M533" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A534" t="s">
         <v>89</v>
       </c>
@@ -45331,10 +46977,13 @@
         <v>18.8</v>
       </c>
       <c r="L534" t="s">
+        <v>544</v>
+      </c>
+      <c r="M534" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A535" t="s">
         <v>89</v>
       </c>
@@ -45369,10 +47018,13 @@
         <v>19.100000000000001</v>
       </c>
       <c r="L535" t="s">
+        <v>544</v>
+      </c>
+      <c r="M535" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A536" t="s">
         <v>89</v>
       </c>
@@ -45407,10 +47059,13 @@
         <v>19.399999999999999</v>
       </c>
       <c r="L536" t="s">
+        <v>544</v>
+      </c>
+      <c r="M536" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="537" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A537" t="s">
         <v>89</v>
       </c>
@@ -45445,10 +47100,13 @@
         <v>19.7</v>
       </c>
       <c r="L537" t="s">
+        <v>544</v>
+      </c>
+      <c r="M537" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A538" t="s">
         <v>89</v>
       </c>
@@ -45483,10 +47141,13 @@
         <v>20.3</v>
       </c>
       <c r="L538" t="s">
+        <v>544</v>
+      </c>
+      <c r="M538" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A539" t="s">
         <v>89</v>
       </c>
@@ -45521,10 +47182,13 @@
         <v>20.9</v>
       </c>
       <c r="L539" t="s">
+        <v>544</v>
+      </c>
+      <c r="M539" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A540" t="s">
         <v>89</v>
       </c>
@@ -45559,10 +47223,13 @@
         <v>27</v>
       </c>
       <c r="L540" t="s">
+        <v>549</v>
+      </c>
+      <c r="M540" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="541" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A541" t="s">
         <v>89</v>
       </c>
@@ -45597,10 +47264,13 @@
         <v>27.5</v>
       </c>
       <c r="L541" t="s">
+        <v>549</v>
+      </c>
+      <c r="M541" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="542" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A542" t="s">
         <v>89</v>
       </c>
@@ -45635,10 +47305,13 @@
         <v>28.5</v>
       </c>
       <c r="L542" t="s">
+        <v>549</v>
+      </c>
+      <c r="M542" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="543" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A543" t="s">
         <v>89</v>
       </c>
@@ -45673,10 +47346,13 @@
         <v>29.5</v>
       </c>
       <c r="L543" t="s">
+        <v>549</v>
+      </c>
+      <c r="M543" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="544" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A544" t="s">
         <v>89</v>
       </c>
@@ -45711,10 +47387,13 @@
         <v>30.5</v>
       </c>
       <c r="L544" t="s">
+        <v>549</v>
+      </c>
+      <c r="M544" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A545" t="s">
         <v>89</v>
       </c>
@@ -45749,10 +47428,13 @@
         <v>31.5</v>
       </c>
       <c r="L545" t="s">
+        <v>549</v>
+      </c>
+      <c r="M545" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A546" t="s">
         <v>89</v>
       </c>
@@ -45787,10 +47469,13 @@
         <v>32.75</v>
       </c>
       <c r="L546" t="s">
+        <v>549</v>
+      </c>
+      <c r="M546" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A547" t="s">
         <v>89</v>
       </c>
@@ -45825,10 +47510,13 @@
         <v>22</v>
       </c>
       <c r="L547" t="s">
+        <v>544</v>
+      </c>
+      <c r="M547" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A548" t="s">
         <v>89</v>
       </c>
@@ -45863,10 +47551,13 @@
         <v>22.5</v>
       </c>
       <c r="L548" t="s">
+        <v>544</v>
+      </c>
+      <c r="M548" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A549" t="s">
         <v>89</v>
       </c>
@@ -45901,10 +47592,13 @@
         <v>23</v>
       </c>
       <c r="L549" t="s">
+        <v>544</v>
+      </c>
+      <c r="M549" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A550" t="s">
         <v>89</v>
       </c>
@@ -45939,10 +47633,13 @@
         <v>23.5</v>
       </c>
       <c r="L550" t="s">
+        <v>544</v>
+      </c>
+      <c r="M550" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A551" t="s">
         <v>89</v>
       </c>
@@ -45977,10 +47674,13 @@
         <v>24</v>
       </c>
       <c r="L551" t="s">
+        <v>544</v>
+      </c>
+      <c r="M551" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A552" t="s">
         <v>89</v>
       </c>
@@ -46015,10 +47715,13 @@
         <v>24.5</v>
       </c>
       <c r="L552" t="s">
+        <v>544</v>
+      </c>
+      <c r="M552" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A553" t="s">
         <v>89</v>
       </c>
@@ -46053,10 +47756,13 @@
         <v>25</v>
       </c>
       <c r="L553" t="s">
+        <v>544</v>
+      </c>
+      <c r="M553" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A554" t="s">
         <v>89</v>
       </c>
@@ -46091,10 +47797,13 @@
         <v>25.5</v>
       </c>
       <c r="L554" t="s">
+        <v>544</v>
+      </c>
+      <c r="M554" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A555" t="s">
         <v>89</v>
       </c>
@@ -46129,10 +47838,13 @@
         <v>26</v>
       </c>
       <c r="L555" t="s">
+        <v>544</v>
+      </c>
+      <c r="M555" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A556" t="s">
         <v>89</v>
       </c>
@@ -46167,10 +47879,13 @@
         <v>26.5</v>
       </c>
       <c r="L556" t="s">
+        <v>544</v>
+      </c>
+      <c r="M556" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A557" t="s">
         <v>89</v>
       </c>
@@ -46205,10 +47920,13 @@
         <v>27</v>
       </c>
       <c r="L557" t="s">
+        <v>544</v>
+      </c>
+      <c r="M557" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A558" t="s">
         <v>89</v>
       </c>
@@ -46243,10 +47961,13 @@
         <v>16.399999999999999</v>
       </c>
       <c r="L558" t="s">
+        <v>544</v>
+      </c>
+      <c r="M558" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A559" t="s">
         <v>89</v>
       </c>
@@ -46281,10 +48002,13 @@
         <v>16.7</v>
       </c>
       <c r="L559" t="s">
+        <v>544</v>
+      </c>
+      <c r="M559" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A560" t="s">
         <v>89</v>
       </c>
@@ -46319,10 +48043,13 @@
         <v>17</v>
       </c>
       <c r="L560" t="s">
+        <v>544</v>
+      </c>
+      <c r="M560" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A561" t="s">
         <v>89</v>
       </c>
@@ -46357,10 +48084,13 @@
         <v>17.3</v>
       </c>
       <c r="L561" t="s">
+        <v>544</v>
+      </c>
+      <c r="M561" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A562" t="s">
         <v>89</v>
       </c>
@@ -46395,10 +48125,13 @@
         <v>17.600000000000001</v>
       </c>
       <c r="L562" t="s">
+        <v>544</v>
+      </c>
+      <c r="M562" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A563" t="s">
         <v>89</v>
       </c>
@@ -46433,10 +48166,13 @@
         <v>17.899999999999999</v>
       </c>
       <c r="L563" t="s">
+        <v>544</v>
+      </c>
+      <c r="M563" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A564" t="s">
         <v>89</v>
       </c>
@@ -46471,10 +48207,13 @@
         <v>18.2</v>
       </c>
       <c r="L564" t="s">
+        <v>544</v>
+      </c>
+      <c r="M564" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A565" t="s">
         <v>89</v>
       </c>
@@ -46509,10 +48248,13 @@
         <v>18.5</v>
       </c>
       <c r="L565" t="s">
+        <v>544</v>
+      </c>
+      <c r="M565" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A566" t="s">
         <v>89</v>
       </c>
@@ -46547,10 +48289,13 @@
         <v>18.8</v>
       </c>
       <c r="L566" t="s">
+        <v>544</v>
+      </c>
+      <c r="M566" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A567" t="s">
         <v>89</v>
       </c>
@@ -46585,10 +48330,13 @@
         <v>26</v>
       </c>
       <c r="L567" t="s">
+        <v>549</v>
+      </c>
+      <c r="M567" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="568" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A568" t="s">
         <v>89</v>
       </c>
@@ -46623,10 +48371,13 @@
         <v>26.5</v>
       </c>
       <c r="L568" t="s">
+        <v>549</v>
+      </c>
+      <c r="M568" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A569" t="s">
         <v>89</v>
       </c>
@@ -46661,10 +48412,13 @@
         <v>27</v>
       </c>
       <c r="L569" t="s">
+        <v>549</v>
+      </c>
+      <c r="M569" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A570" t="s">
         <v>89</v>
       </c>
@@ -46699,10 +48453,13 @@
         <v>27.5</v>
       </c>
       <c r="L570" t="s">
+        <v>549</v>
+      </c>
+      <c r="M570" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A571" t="s">
         <v>89</v>
       </c>
@@ -46737,10 +48494,13 @@
         <v>28</v>
       </c>
       <c r="L571" t="s">
+        <v>549</v>
+      </c>
+      <c r="M571" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A572" t="s">
         <v>89</v>
       </c>
@@ -46775,10 +48535,13 @@
         <v>28.5</v>
       </c>
       <c r="L572" t="s">
+        <v>549</v>
+      </c>
+      <c r="M572" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A573" t="s">
         <v>89</v>
       </c>
@@ -46813,10 +48576,13 @@
         <v>29</v>
       </c>
       <c r="L573" t="s">
+        <v>549</v>
+      </c>
+      <c r="M573" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A574" t="s">
         <v>89</v>
       </c>
@@ -46851,6 +48617,9 @@
         <v>29.5</v>
       </c>
       <c r="L574" t="s">
+        <v>549</v>
+      </c>
+      <c r="M574" t="s">
         <v>488</v>
       </c>
     </row>
